--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -203,6 +203,9 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -218,9 +221,6 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
@@ -239,15 +239,6 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -257,63 +248,48 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>COSSIO</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
     <t>LIA SARED</t>
   </si>
   <si>
@@ -323,16 +299,16 @@
     <t>AMISADAY</t>
   </si>
   <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
     <t>SANDRA PAOLA</t>
   </si>
   <si>
     <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>BRAYAN JOSUE</t>
-  </si>
-  <si>
-    <t>MARIA ESTELA</t>
   </si>
 </sst>
 </file>
@@ -878,25 +854,25 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -941,10 +917,10 @@
         <v>6</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -979,25 +955,25 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1027,16 +1003,16 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>8</v>
@@ -1045,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="AF5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1080,25 +1056,25 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1128,22 +1104,22 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD6">
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1181,25 +1157,25 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1229,13 +1205,13 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>8</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1247,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1282,25 +1258,25 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1330,16 +1306,16 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>5</v>
@@ -1383,25 +1359,25 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1431,13 +1407,13 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -1484,25 +1460,25 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1532,13 +1508,13 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1585,25 +1561,25 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1636,7 +1612,7 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>5</v>
@@ -1686,25 +1662,25 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1734,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1749,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="AE12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12">
         <v>8</v>
@@ -1787,25 +1763,25 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1835,7 +1811,7 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1850,10 +1826,10 @@
         <v>5</v>
       </c>
       <c r="AE13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1888,25 +1864,25 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1939,7 +1915,7 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -1951,7 +1927,7 @@
         <v>9</v>
       </c>
       <c r="AE14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>5</v>
@@ -1989,25 +1965,25 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -2037,13 +2013,13 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>6</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -2090,25 +2066,25 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2138,7 +2114,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2191,25 +2167,25 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2242,10 +2218,10 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2274,7 +2250,7 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -2292,25 +2268,25 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2340,13 +2316,13 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2393,25 +2369,25 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2441,13 +2417,13 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2456,7 +2432,7 @@
         <v>7</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -2494,25 +2470,25 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2542,22 +2518,22 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD20">
         <v>8</v>
       </c>
       <c r="AE20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF20">
         <v>6</v>
@@ -2595,25 +2571,25 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2643,7 +2619,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2652,7 +2628,7 @@
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD21">
         <v>9</v>
@@ -2696,25 +2672,25 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2744,16 +2720,16 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>9</v>
@@ -2762,7 +2738,7 @@
         <v>9</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2797,25 +2773,25 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2845,16 +2821,16 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>9</v>
@@ -2898,25 +2874,25 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2999,25 +2975,25 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -3047,10 +3023,10 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -3065,7 +3041,7 @@
         <v>9</v>
       </c>
       <c r="AF25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3100,25 +3076,25 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -3148,13 +3124,13 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>5</v>
@@ -3201,25 +3177,25 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -3249,7 +3225,7 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -3258,7 +3234,7 @@
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD27">
         <v>8</v>
@@ -3267,7 +3243,7 @@
         <v>6</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3302,25 +3278,25 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3350,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>8</v>
@@ -3368,7 +3344,7 @@
         <v>6</v>
       </c>
       <c r="AF28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3403,25 +3379,25 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3451,7 +3427,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3460,7 +3436,7 @@
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD29">
         <v>7</v>
@@ -3504,25 +3480,25 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3552,22 +3528,22 @@
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD30">
         <v>6</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30">
         <v>7</v>
@@ -3605,25 +3581,25 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3653,13 +3629,13 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3706,25 +3682,25 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3807,25 +3783,25 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3855,22 +3831,22 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>9</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD33">
         <v>9</v>
       </c>
       <c r="AE33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF33">
         <v>10</v>
@@ -3908,25 +3884,25 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -4009,25 +3985,25 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -4057,10 +4033,10 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>5</v>
@@ -4072,7 +4048,7 @@
         <v>6</v>
       </c>
       <c r="AE35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF35">
         <v>5</v>
@@ -4110,25 +4086,25 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -4158,25 +4134,25 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB36">
         <v>6</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD36">
         <v>7</v>
       </c>
       <c r="AE36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4211,25 +4187,25 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -4274,7 +4250,7 @@
         <v>6</v>
       </c>
       <c r="AE37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF37">
         <v>5</v>
@@ -4452,10 +4428,10 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N4">
         <v>95</v>
@@ -4476,10 +4452,10 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V4">
         <v>95</v>
@@ -4523,7 +4499,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -4547,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4600,13 +4576,13 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -4624,13 +4600,13 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4683,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4707,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4754,13 +4730,13 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4769,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4778,13 +4754,13 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -4793,7 +4769,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -4831,13 +4807,13 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4855,13 +4831,13 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -4908,22 +4884,22 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4932,22 +4908,22 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X10">
         <v>100</v>
@@ -4985,13 +4961,13 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M11">
         <v>93.8</v>
@@ -5000,7 +4976,7 @@
         <v>95</v>
       </c>
       <c r="O11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -5009,13 +4985,13 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U11">
         <v>93.8</v>
@@ -5024,7 +5000,7 @@
         <v>95</v>
       </c>
       <c r="W11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -5062,22 +5038,22 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>95</v>
+        <v>77.3</v>
       </c>
       <c r="M12">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N12">
         <v>90</v>
       </c>
       <c r="O12">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -5086,22 +5062,22 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95</v>
+        <v>77.3</v>
       </c>
       <c r="U12">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V12">
         <v>90</v>
       </c>
       <c r="W12">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X12">
         <v>100</v>
@@ -5139,46 +5115,46 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>79.5</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>80</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>79.5</v>
+      </c>
+      <c r="U13">
         <v>93.8</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>60</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
-        <v>95</v>
-      </c>
-      <c r="U13">
-        <v>100</v>
-      </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -5216,13 +5192,13 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -5240,13 +5216,13 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -5293,16 +5269,16 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N15">
         <v>95</v>
@@ -5317,16 +5293,16 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V15">
         <v>95</v>
@@ -5376,7 +5352,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5400,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -5447,22 +5423,22 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M17">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="N17">
         <v>100</v>
       </c>
       <c r="O17">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -5471,22 +5447,22 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U17">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -5530,10 +5506,10 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="M18">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N18">
         <v>95</v>
@@ -5554,10 +5530,10 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="U18">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V18">
         <v>95</v>
@@ -5607,7 +5583,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>95</v>
+        <v>81.8</v>
       </c>
       <c r="M19">
         <v>87.5</v>
@@ -5616,7 +5592,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -5631,7 +5607,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>95</v>
+        <v>81.8</v>
       </c>
       <c r="U19">
         <v>87.5</v>
@@ -5640,7 +5616,7 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -5678,13 +5654,13 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -5693,7 +5669,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -5702,13 +5678,13 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -5717,7 +5693,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -5761,7 +5737,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5785,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -5838,7 +5814,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -5862,7 +5838,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5909,13 +5885,13 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -5933,13 +5909,13 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5986,13 +5962,13 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -6010,13 +5986,13 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S24">
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -6069,7 +6045,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -6093,7 +6069,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6140,16 +6116,16 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M26">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N26">
         <v>90</v>
@@ -6164,16 +6140,16 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V26">
         <v>90</v>
@@ -6217,13 +6193,13 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -6241,13 +6217,13 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6294,13 +6270,13 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -6309,7 +6285,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -6318,13 +6294,13 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -6333,7 +6309,7 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -6371,16 +6347,16 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -6395,16 +6371,16 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6448,16 +6424,16 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -6472,16 +6448,16 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6531,10 +6507,10 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -6555,10 +6531,10 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6602,22 +6578,22 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>95</v>
+        <v>79.5</v>
       </c>
       <c r="M32">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N32">
         <v>100</v>
       </c>
       <c r="O32">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -6626,22 +6602,22 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="S32">
         <v>100</v>
       </c>
       <c r="T32">
-        <v>95</v>
+        <v>79.5</v>
       </c>
       <c r="U32">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V32">
         <v>100</v>
       </c>
       <c r="W32">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X32">
         <v>100</v>
@@ -6679,13 +6655,13 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -6694,7 +6670,7 @@
         <v>90</v>
       </c>
       <c r="O33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6703,13 +6679,13 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S33">
         <v>100</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -6718,7 +6694,7 @@
         <v>90</v>
       </c>
       <c r="W33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X33">
         <v>100</v>
@@ -6756,16 +6732,16 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>95</v>
+        <v>43.2</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="N34">
         <v>85</v>
@@ -6774,22 +6750,22 @@
         <v>12.5</v>
       </c>
       <c r="P34">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S34">
         <v>100</v>
       </c>
       <c r="T34">
-        <v>95</v>
+        <v>43.2</v>
       </c>
       <c r="U34">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="V34">
         <v>85</v>
@@ -6798,7 +6774,7 @@
         <v>12.5</v>
       </c>
       <c r="X34">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Y34">
         <v>100</v>
@@ -6833,22 +6809,22 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N35">
         <v>100</v>
       </c>
       <c r="O35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -6857,22 +6833,22 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S35">
         <v>100</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U35">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V35">
         <v>100</v>
       </c>
       <c r="W35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X35">
         <v>100</v>
@@ -6910,13 +6886,13 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -6934,13 +6910,13 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S36">
         <v>100</v>
       </c>
       <c r="T36">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -6987,22 +6963,22 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N37">
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -7011,22 +6987,22 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S37">
         <v>100</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V37">
         <v>100</v>
       </c>
       <c r="W37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X37">
         <v>100</v>
@@ -7098,19 +7074,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2">
-        <v>32.4</v>
+        <v>35.3</v>
       </c>
       <c r="G2" s="2">
-        <v>67.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7121,7 +7097,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -7130,19 +7106,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2">
-        <v>55.9</v>
+        <v>38.2</v>
       </c>
       <c r="G3" s="2">
-        <v>44.1</v>
+        <v>61.8</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7153,7 +7129,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -7162,19 +7138,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
-        <v>67.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2">
-        <v>32.4</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7185,7 +7161,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -7206,7 +7182,7 @@
         <v>32.4</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7217,7 +7193,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -7226,19 +7202,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>73.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>26.5</v>
+        <v>32.4</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7249,7 +7225,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -7258,19 +7234,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>88.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>11.8</v>
+        <v>17.6</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7281,7 +7257,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -7290,19 +7266,19 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="G8" s="2">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7384,7 +7360,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7422,16 +7398,16 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7445,10 +7421,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7462,22 +7438,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920400</v>
+        <v>24330051920170</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7485,22 +7461,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920400</v>
+        <v>24330051920170</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7508,22 +7484,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920298</v>
+        <v>24330051920174</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7531,22 +7507,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920298</v>
+        <v>24330051920174</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7554,22 +7530,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920188</v>
+        <v>24330051920182</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7577,22 +7553,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920188</v>
+        <v>24330051920182</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7600,22 +7576,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920170</v>
+        <v>24330051920206</v>
       </c>
       <c r="B10" t="s">
         <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7623,16 +7599,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920174</v>
+        <v>24330051920206</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7646,22 +7622,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920182</v>
+        <v>24330051920277</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7669,22 +7645,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920184</v>
+        <v>24330051920277</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7692,22 +7668,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920206</v>
+        <v>24330051920180</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7715,22 +7691,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920190</v>
+        <v>24330051920184</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7738,47 +7714,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920402</v>
+        <v>24330051920190</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920076</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -209,16 +209,16 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -236,15 +236,15 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -254,21 +254,18 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>HILARIO</t>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -278,37 +275,34 @@
     <t>TLAXCALTECA</t>
   </si>
   <si>
-    <t>APALE</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ORTEGA</t>
+    <t>LIA SARED</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>AMISADAY</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
-  </si>
-  <si>
     <t>GAEL ARMANDO</t>
   </si>
   <si>
-    <t>MARLENE</t>
+    <t>OCTAVIO</t>
   </si>
   <si>
     <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
   </si>
 </sst>
 </file>
@@ -866,7 +860,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>8</v>
@@ -914,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE4">
         <v>9</v>
@@ -967,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -1015,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="AD5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE5">
         <v>9</v>
@@ -1068,7 +1062,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1169,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>8</v>
@@ -1217,7 +1211,7 @@
         <v>5</v>
       </c>
       <c r="AD7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE7">
         <v>8</v>
@@ -1270,7 +1264,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1371,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1472,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>7</v>
@@ -1520,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10">
         <v>7</v>
@@ -1573,7 +1567,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1674,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>7</v>
@@ -1775,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1876,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1977,7 +1971,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>9</v>
@@ -2025,7 +2019,7 @@
         <v>6</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE15">
         <v>9</v>
@@ -2078,7 +2072,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -2179,7 +2173,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -2280,7 +2274,7 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>8</v>
@@ -2328,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE18">
         <v>9</v>
@@ -2381,7 +2375,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2429,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE19">
         <v>9</v>
@@ -2482,7 +2476,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>9</v>
@@ -2583,7 +2577,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>9</v>
@@ -2684,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>9</v>
@@ -2732,7 +2726,7 @@
         <v>7</v>
       </c>
       <c r="AD22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE22">
         <v>9</v>
@@ -2785,7 +2779,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -2833,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE23">
         <v>9</v>
@@ -2886,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>7</v>
@@ -2987,7 +2981,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>8</v>
@@ -3035,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE25">
         <v>9</v>
@@ -3088,7 +3082,7 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>7</v>
@@ -3189,7 +3183,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -3290,7 +3284,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -3338,7 +3332,7 @@
         <v>5</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE28">
         <v>6</v>
@@ -3391,7 +3385,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>7</v>
@@ -3439,7 +3433,7 @@
         <v>5</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE29">
         <v>8</v>
@@ -3492,7 +3486,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>8</v>
@@ -3540,7 +3534,7 @@
         <v>7</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE30">
         <v>9</v>
@@ -3593,7 +3587,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -3694,7 +3688,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -3795,7 +3789,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>9</v>
@@ -3843,7 +3837,7 @@
         <v>7</v>
       </c>
       <c r="AD33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE33">
         <v>8</v>
@@ -3896,7 +3890,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>5</v>
@@ -3997,7 +3991,7 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>8</v>
@@ -4098,7 +4092,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>9</v>
@@ -4146,7 +4140,7 @@
         <v>7</v>
       </c>
       <c r="AD36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE36">
         <v>9</v>
@@ -4199,7 +4193,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -4247,7 +4241,7 @@
         <v>5</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE37">
         <v>8</v>
@@ -4434,7 +4428,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="N4">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -4458,7 +4452,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V4">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W4">
         <v>100</v>
@@ -4973,7 +4967,7 @@
         <v>93.8</v>
       </c>
       <c r="N11">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O11">
         <v>96.90000000000001</v>
@@ -4997,7 +4991,7 @@
         <v>93.8</v>
       </c>
       <c r="V11">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W11">
         <v>96.90000000000001</v>
@@ -5050,7 +5044,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="N12">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O12">
         <v>93.8</v>
@@ -5074,7 +5068,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V12">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W12">
         <v>93.8</v>
@@ -5281,7 +5275,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -5305,7 +5299,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W15">
         <v>100</v>
@@ -5358,7 +5352,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>50</v>
+        <v>76.2</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -5382,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>50</v>
+        <v>76.2</v>
       </c>
       <c r="W16">
         <v>100</v>
@@ -5512,7 +5506,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N18">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -5536,7 +5530,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V18">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W18">
         <v>100</v>
@@ -6128,7 +6122,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N26">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -6152,7 +6146,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W26">
         <v>100</v>
@@ -6667,7 +6661,7 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O33">
         <v>96.90000000000001</v>
@@ -6691,7 +6685,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W33">
         <v>96.90000000000001</v>
@@ -6744,7 +6738,7 @@
         <v>81.3</v>
       </c>
       <c r="N34">
-        <v>85</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O34">
         <v>12.5</v>
@@ -6768,7 +6762,7 @@
         <v>81.3</v>
       </c>
       <c r="V34">
-        <v>85</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W34">
         <v>12.5</v>
@@ -7161,7 +7155,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -7170,19 +7164,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2">
-        <v>67.59999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="G5" s="2">
-        <v>32.4</v>
+        <v>47.1</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7193,7 +7187,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -7214,7 +7208,7 @@
         <v>32.4</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7392,22 +7386,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920308</v>
+        <v>24330051920170</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7415,16 +7409,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920308</v>
+        <v>24330051920170</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7438,22 +7432,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920170</v>
+        <v>24330051920174</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7461,16 +7455,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920170</v>
+        <v>24330051920174</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -7484,22 +7478,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920174</v>
+        <v>24330051920180</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7507,22 +7501,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920174</v>
+        <v>24330051920180</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7536,10 +7530,10 @@
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -7559,10 +7553,10 @@
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7582,10 +7576,10 @@
         <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -7605,10 +7599,10 @@
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7628,10 +7622,10 @@
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -7651,10 +7645,10 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -7668,16 +7662,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920180</v>
+        <v>24330051920190</v>
       </c>
       <c r="B14" t="s">
         <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -7691,22 +7685,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920184</v>
+        <v>24330051920190</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7714,16 +7708,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920190</v>
+        <v>24330051920184</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -215,15 +215,15 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -239,13 +239,10 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>HILARIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>PORTUGAL</t>
@@ -257,16 +254,10 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>VEGA</t>
@@ -278,19 +269,13 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>LIA SARED</t>
   </si>
   <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
     <t>MARLENE</t>
   </si>
   <si>
-    <t>AMISADAY</t>
+    <t>SANDRA PAOLA</t>
   </si>
   <si>
     <t>SANTIAGO</t>
@@ -300,9 +285,6 @@
   </si>
   <si>
     <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -869,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -970,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1071,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1172,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1273,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1321,7 +1303,7 @@
         <v>5</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -1374,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1475,7 +1457,7 @@
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1523,7 +1505,7 @@
         <v>6</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -1576,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1624,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1677,7 +1659,7 @@
         <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1725,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="AG12">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -1778,7 +1760,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1879,7 +1861,7 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1927,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="AG14">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -1980,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2081,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2129,7 +2111,7 @@
         <v>5</v>
       </c>
       <c r="AG16">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:33">
@@ -2182,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2230,7 +2212,7 @@
         <v>7</v>
       </c>
       <c r="AG17">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -2283,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2331,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2384,7 +2366,7 @@
         <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2485,7 +2467,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2586,7 +2568,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2687,7 +2669,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2735,7 +2717,7 @@
         <v>8</v>
       </c>
       <c r="AG22">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:33">
@@ -2788,7 +2770,7 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2889,7 +2871,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2990,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3091,7 +3073,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3192,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3293,7 +3275,7 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3394,7 +3376,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3495,7 +3477,7 @@
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3596,7 +3578,7 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3697,7 +3679,7 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3745,7 +3727,7 @@
         <v>5</v>
       </c>
       <c r="AG32">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:33">
@@ -3798,7 +3780,7 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3899,7 +3881,7 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3947,7 +3929,7 @@
         <v>5</v>
       </c>
       <c r="AG34">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:33">
@@ -4000,7 +3982,7 @@
         <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4101,7 +4083,7 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4202,7 +4184,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4437,7 +4419,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R4">
         <v>90</v>
@@ -4461,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="Y4">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -4591,7 +4573,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R6">
         <v>75</v>
@@ -4615,7 +4597,7 @@
         <v>100</v>
       </c>
       <c r="Y6">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -4668,7 +4650,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4692,7 +4674,7 @@
         <v>100</v>
       </c>
       <c r="Y7">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -4745,7 +4727,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R8">
         <v>65</v>
@@ -4769,7 +4751,7 @@
         <v>100</v>
       </c>
       <c r="Y8">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -4822,7 +4804,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R9">
         <v>95</v>
@@ -4846,7 +4828,7 @@
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -4899,7 +4881,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10">
         <v>80</v>
@@ -4923,7 +4905,7 @@
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -4976,7 +4958,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R11">
         <v>75</v>
@@ -5000,7 +4982,7 @@
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -5053,7 +5035,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R12">
         <v>55</v>
@@ -5077,7 +5059,7 @@
         <v>100</v>
       </c>
       <c r="Y12">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -5130,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R13">
         <v>80</v>
@@ -5154,7 +5136,7 @@
         <v>100</v>
       </c>
       <c r="Y13">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -5207,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R14">
         <v>80</v>
@@ -5231,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="Y14">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -5361,7 +5343,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5385,7 +5367,7 @@
         <v>100</v>
       </c>
       <c r="Y16">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -5438,7 +5420,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R17">
         <v>80</v>
@@ -5462,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="Y17">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -5515,7 +5497,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R18">
         <v>70</v>
@@ -5539,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="Y18">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -5669,7 +5651,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R20">
         <v>90</v>
@@ -5693,7 +5675,7 @@
         <v>100</v>
       </c>
       <c r="Y20">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -5746,7 +5728,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5770,7 +5752,7 @@
         <v>100</v>
       </c>
       <c r="Y21">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -5823,7 +5805,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5847,7 +5829,7 @@
         <v>100</v>
       </c>
       <c r="Y22">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -5977,7 +5959,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R24">
         <v>85</v>
@@ -6001,7 +5983,7 @@
         <v>100</v>
       </c>
       <c r="Y24">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -6054,7 +6036,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R25">
         <v>80</v>
@@ -6078,7 +6060,7 @@
         <v>100</v>
       </c>
       <c r="Y25">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -6131,7 +6113,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R26">
         <v>75</v>
@@ -6155,7 +6137,7 @@
         <v>100</v>
       </c>
       <c r="Y26">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -6208,7 +6190,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R27">
         <v>70</v>
@@ -6232,7 +6214,7 @@
         <v>100</v>
       </c>
       <c r="Y27">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -6285,7 +6267,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R28">
         <v>95</v>
@@ -6309,7 +6291,7 @@
         <v>100</v>
       </c>
       <c r="Y28">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -6439,7 +6421,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R30">
         <v>85</v>
@@ -6463,7 +6445,7 @@
         <v>100</v>
       </c>
       <c r="Y30">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -6516,7 +6498,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R31">
         <v>70</v>
@@ -6540,7 +6522,7 @@
         <v>100</v>
       </c>
       <c r="Y31">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -6593,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R32">
         <v>75</v>
@@ -6617,7 +6599,7 @@
         <v>100</v>
       </c>
       <c r="Y32">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -6670,7 +6652,7 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R33">
         <v>95</v>
@@ -6694,7 +6676,7 @@
         <v>100</v>
       </c>
       <c r="Y33">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -6747,7 +6729,7 @@
         <v>25</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R34">
         <v>70</v>
@@ -6771,7 +6753,7 @@
         <v>25</v>
       </c>
       <c r="Y34">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -6824,7 +6806,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R35">
         <v>75</v>
@@ -6848,7 +6830,7 @@
         <v>100</v>
       </c>
       <c r="Y35">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -6901,7 +6883,7 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R36">
         <v>85</v>
@@ -6925,7 +6907,7 @@
         <v>100</v>
       </c>
       <c r="Y36">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -7219,7 +7201,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -7228,19 +7210,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2">
-        <v>82.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>17.6</v>
+        <v>32.4</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7251,7 +7233,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -7260,19 +7242,19 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>91.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>8.800000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7283,7 +7265,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
@@ -7292,19 +7274,19 @@
         <v>34</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7354,7 +7336,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7395,7 +7377,7 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7418,7 +7400,7 @@
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7432,22 +7414,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920174</v>
+        <v>24330051920180</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7455,22 +7437,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920174</v>
+        <v>24330051920180</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7478,16 +7460,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920180</v>
+        <v>24330051920184</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7501,22 +7483,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920180</v>
+        <v>24330051920184</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7524,22 +7506,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920182</v>
+        <v>24330051920206</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7547,16 +7529,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920182</v>
+        <v>24330051920206</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7570,16 +7552,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920206</v>
+        <v>24330051920277</v>
       </c>
       <c r="B10" t="s">
         <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -7593,16 +7575,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920206</v>
+        <v>24330051920277</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7616,16 +7598,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920277</v>
+        <v>24330051920190</v>
       </c>
       <c r="B12" t="s">
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -7639,93 +7621,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920277</v>
+        <v>24330051920190</v>
       </c>
       <c r="B13" t="s">
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920190</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920190</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920184</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -56,150 +56,150 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>AGUILAR COSSIO SANTIAGO</t>
+  </si>
+  <si>
+    <t>ANASTACIO HERNANDEZ ANA LAURA</t>
+  </si>
+  <si>
+    <t>CALIHUA GALLARDO MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>CARRERA CARRERA LIA SARED</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA VIEYRA MARIEL</t>
+  </si>
+  <si>
+    <t>CID SOL DANIELA</t>
+  </si>
+  <si>
+    <t>FLORES VILLA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>GUERRA BRAVO SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>GUZMAN SANCHEZ DANIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ CRUZ SAUL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ SANCHEZ JHOCELIN VALENTINA</t>
+  </si>
+  <si>
+    <t>HILARIO APALE MARLENE</t>
+  </si>
+  <si>
+    <t>JUAREZ LIBRADO YURANI</t>
+  </si>
+  <si>
+    <t>LOPEZ DE LA CRUZ AMISADAY</t>
+  </si>
+  <si>
+    <t>LOPEZ GONZALEZ JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>MAZA ENCARNACION KEVIN JESUS</t>
+  </si>
+  <si>
+    <t>MORALES HERNANDEZ ALLYSON AILANI</t>
+  </si>
+  <si>
+    <t>MORALES SOTO KRISTEN DAMARIS</t>
+  </si>
+  <si>
+    <t>MORALES TRUJILLO SANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>MORENO ROSAS IRAIS</t>
+  </si>
+  <si>
+    <t>MUÑOZ MUÑOZ IRVING EMILIO</t>
+  </si>
+  <si>
+    <t>OSORIO HERNANDEZ AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>PELLICO REYES BENJAMIN</t>
+  </si>
+  <si>
+    <t>PICHARDO TEPOLE JIMENA</t>
+  </si>
+  <si>
+    <t>PORTUGAL VEGA SANTIAGO</t>
+  </si>
+  <si>
+    <t>REYES TLAXCALTECA GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ROSAS ORTEGA OCTAVIO</t>
+  </si>
+  <si>
+    <t>SOTO ZOPILLAXTLE LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>TREJO CACERES MEREDY SEYLIN</t>
+  </si>
+  <si>
+    <t>VALENCIA LOPEZ BRAYAN JOSUE</t>
+  </si>
+  <si>
+    <t>VASQUEZ LARA MARISA ITZEL</t>
+  </si>
+  <si>
+    <t>VAZQUEZ MONTIEL BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA MARTINEZ MARIA ESTELA</t>
+  </si>
+  <si>
+    <t>ZENDEJAS SANDOVAL EVAN LAEL</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Docente</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Aprobados</t>
+  </si>
+  <si>
+    <t>Reprobados</t>
+  </si>
+  <si>
+    <t>Por_Apro</t>
+  </si>
+  <si>
+    <t>Por_Repro</t>
+  </si>
+  <si>
+    <t>Promedio</t>
+  </si>
+  <si>
+    <t>Blancos</t>
+  </si>
+  <si>
+    <t>Por_Blancos</t>
+  </si>
+  <si>
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>AGUILAR COSSIO SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANASTACIO HERNANDEZ ANA LAURA</t>
-  </si>
-  <si>
-    <t>CALIHUA GALLARDO MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>CARRERA CARRERA LIA SARED</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA VIEYRA MARIEL</t>
-  </si>
-  <si>
-    <t>CID SOL DANIELA</t>
-  </si>
-  <si>
-    <t>FLORES VILLA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>GUERRA BRAVO SANDY CAMILA</t>
-  </si>
-  <si>
-    <t>GUZMAN SANCHEZ DANIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ CRUZ SAUL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ SANCHEZ JHOCELIN VALENTINA</t>
-  </si>
-  <si>
-    <t>HILARIO APALE MARLENE</t>
-  </si>
-  <si>
-    <t>JUAREZ LIBRADO YURANI</t>
-  </si>
-  <si>
-    <t>LOPEZ DE LA CRUZ AMISADAY</t>
-  </si>
-  <si>
-    <t>LOPEZ GONZALEZ JANNIHA YUVIETH</t>
-  </si>
-  <si>
-    <t>MAZA ENCARNACION KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>MORALES HERNANDEZ ALLYSON AILANI</t>
-  </si>
-  <si>
-    <t>MORALES SOTO KRISTEN DAMARIS</t>
-  </si>
-  <si>
-    <t>MORALES TRUJILLO SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>MORENO ROSAS IRAIS</t>
-  </si>
-  <si>
-    <t>MUÑOZ MUÑOZ IRVING EMILIO</t>
-  </si>
-  <si>
-    <t>OSORIO HERNANDEZ AYLIN ABIGAIL</t>
-  </si>
-  <si>
-    <t>PELLICO REYES BENJAMIN</t>
-  </si>
-  <si>
-    <t>PICHARDO TEPOLE JIMENA</t>
-  </si>
-  <si>
-    <t>PORTUGAL VEGA SANTIAGO</t>
-  </si>
-  <si>
-    <t>REYES TLAXCALTECA GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ROSAS ORTEGA OCTAVIO</t>
-  </si>
-  <si>
-    <t>SOTO ZOPILLAXTLE LUZ ARIANA</t>
-  </si>
-  <si>
-    <t>TREJO CACERES MEREDY SEYLIN</t>
-  </si>
-  <si>
-    <t>VALENCIA LOPEZ BRAYAN JOSUE</t>
-  </si>
-  <si>
-    <t>VASQUEZ LARA MARISA ITZEL</t>
-  </si>
-  <si>
-    <t>VAZQUEZ MONTIEL BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA MARTINEZ MARIA ESTELA</t>
-  </si>
-  <si>
-    <t>ZENDEJAS SANDOVAL EVAN LAEL</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>Docente</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Aprobados</t>
-  </si>
-  <si>
-    <t>Reprobados</t>
-  </si>
-  <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
-  </si>
-  <si>
-    <t>Promedio</t>
-  </si>
-  <si>
-    <t>Blancos</t>
-  </si>
-  <si>
-    <t>Por_Blancos</t>
-  </si>
-  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
@@ -215,15 +215,15 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
     <t>NC</t>
   </si>
   <si>
@@ -239,52 +239,70 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>HILARIO</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>LIA SARED</t>
   </si>
   <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
     <t>MARLENE</t>
   </si>
   <si>
+    <t>AMISADAY</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
     <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
   </si>
 </sst>
 </file>
@@ -646,13 +664,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG37"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:29">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -663,39 +681,35 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="W1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-    </row>
-    <row r="2" spans="1:33">
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,89 +735,77 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -827,114 +829,102 @@
         <v>8</v>
       </c>
       <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>8</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <v>8</v>
+      </c>
+      <c r="O4">
+        <v>6</v>
+      </c>
+      <c r="P4">
+        <v>-1</v>
+      </c>
+      <c r="Q4">
+        <v>-1</v>
+      </c>
+      <c r="R4">
+        <v>-1</v>
+      </c>
+      <c r="S4">
+        <v>-1</v>
+      </c>
+      <c r="T4">
+        <v>-1</v>
+      </c>
+      <c r="U4">
+        <v>-1</v>
+      </c>
+      <c r="V4">
+        <v>-1</v>
+      </c>
+      <c r="W4">
+        <v>6</v>
+      </c>
+      <c r="X4">
+        <v>9</v>
+      </c>
+      <c r="Y4">
+        <v>5</v>
+      </c>
+      <c r="Z4">
+        <v>5</v>
+      </c>
+      <c r="AA4">
+        <v>5</v>
+      </c>
+      <c r="AB4">
+        <v>9</v>
+      </c>
+      <c r="AC4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
         <v>10</v>
-      </c>
-      <c r="J4">
-        <v>6</v>
-      </c>
-      <c r="K4">
-        <v>8</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>6</v>
-      </c>
-      <c r="N4">
-        <v>5</v>
-      </c>
-      <c r="O4">
-        <v>8</v>
-      </c>
-      <c r="P4">
-        <v>6</v>
-      </c>
-      <c r="Q4">
-        <v>10</v>
-      </c>
-      <c r="R4">
-        <v>-1</v>
-      </c>
-      <c r="S4">
-        <v>-1</v>
-      </c>
-      <c r="T4">
-        <v>-1</v>
-      </c>
-      <c r="U4">
-        <v>-1</v>
-      </c>
-      <c r="V4">
-        <v>-1</v>
-      </c>
-      <c r="W4">
-        <v>-1</v>
-      </c>
-      <c r="X4">
-        <v>-1</v>
-      </c>
-      <c r="Y4">
-        <v>-1</v>
-      </c>
-      <c r="Z4">
-        <v>6</v>
-      </c>
-      <c r="AA4">
-        <v>9</v>
-      </c>
-      <c r="AB4">
-        <v>5</v>
-      </c>
-      <c r="AC4">
-        <v>5</v>
-      </c>
-      <c r="AD4">
-        <v>5</v>
-      </c>
-      <c r="AE4">
-        <v>9</v>
-      </c>
-      <c r="AF4">
-        <v>7</v>
-      </c>
-      <c r="AG4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -943,16 +933,16 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q5">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -970,13 +960,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>8</v>
@@ -990,123 +980,99 @@
       <c r="AC5">
         <v>8</v>
       </c>
-      <c r="AD5">
-        <v>9</v>
-      </c>
-      <c r="AE5">
-        <v>9</v>
-      </c>
-      <c r="AF5">
-        <v>8</v>
-      </c>
-      <c r="AG5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33">
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <v>-1</v>
+      </c>
+      <c r="Q6">
+        <v>-1</v>
+      </c>
+      <c r="R6">
+        <v>-1</v>
+      </c>
+      <c r="S6">
+        <v>-1</v>
+      </c>
+      <c r="T6">
+        <v>-1</v>
+      </c>
+      <c r="U6">
+        <v>-1</v>
+      </c>
+      <c r="V6">
+        <v>-1</v>
+      </c>
+      <c r="W6">
+        <v>5</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>7</v>
+      </c>
+      <c r="Z6">
+        <v>5</v>
+      </c>
+      <c r="AA6">
+        <v>5</v>
+      </c>
+      <c r="AB6">
+        <v>7</v>
+      </c>
+      <c r="AC6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-      <c r="N6">
-        <v>5</v>
-      </c>
-      <c r="O6">
-        <v>7</v>
-      </c>
-      <c r="P6">
-        <v>5</v>
-      </c>
-      <c r="Q6">
-        <v>10</v>
-      </c>
-      <c r="R6">
-        <v>-1</v>
-      </c>
-      <c r="S6">
-        <v>-1</v>
-      </c>
-      <c r="T6">
-        <v>-1</v>
-      </c>
-      <c r="U6">
-        <v>-1</v>
-      </c>
-      <c r="V6">
-        <v>-1</v>
-      </c>
-      <c r="W6">
-        <v>-1</v>
-      </c>
-      <c r="X6">
-        <v>-1</v>
-      </c>
-      <c r="Y6">
-        <v>-1</v>
-      </c>
-      <c r="Z6">
-        <v>5</v>
-      </c>
-      <c r="AA6">
-        <v>8</v>
-      </c>
-      <c r="AB6">
-        <v>7</v>
-      </c>
-      <c r="AC6">
-        <v>5</v>
-      </c>
-      <c r="AD6">
-        <v>5</v>
-      </c>
-      <c r="AE6">
-        <v>7</v>
-      </c>
-      <c r="AF6">
-        <v>5</v>
-      </c>
-      <c r="AG6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1130,31 +1096,31 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q7">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1172,143 +1138,119 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
-        <v>5</v>
-      </c>
-      <c r="AD7">
-        <v>7</v>
-      </c>
-      <c r="AE7">
-        <v>8</v>
-      </c>
-      <c r="AF7">
-        <v>7</v>
-      </c>
-      <c r="AG7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>7</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+      <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>-1</v>
+      </c>
+      <c r="Q8">
+        <v>-1</v>
+      </c>
+      <c r="R8">
+        <v>-1</v>
+      </c>
+      <c r="S8">
+        <v>-1</v>
+      </c>
+      <c r="T8">
+        <v>-1</v>
+      </c>
+      <c r="U8">
+        <v>-1</v>
+      </c>
+      <c r="V8">
+        <v>-1</v>
+      </c>
+      <c r="W8">
+        <v>5</v>
+      </c>
+      <c r="X8">
+        <v>9</v>
+      </c>
+      <c r="Y8">
+        <v>6</v>
+      </c>
+      <c r="Z8">
+        <v>7</v>
+      </c>
+      <c r="AA8">
+        <v>5</v>
+      </c>
+      <c r="AB8">
+        <v>9</v>
+      </c>
+      <c r="AC8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8">
-        <v>8</v>
-      </c>
-      <c r="L8">
-        <v>7</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
-      </c>
-      <c r="N8">
-        <v>6</v>
-      </c>
-      <c r="O8">
-        <v>8</v>
-      </c>
-      <c r="P8">
-        <v>5</v>
-      </c>
-      <c r="Q8">
-        <v>5</v>
-      </c>
-      <c r="R8">
-        <v>-1</v>
-      </c>
-      <c r="S8">
-        <v>-1</v>
-      </c>
-      <c r="T8">
-        <v>-1</v>
-      </c>
-      <c r="U8">
-        <v>-1</v>
-      </c>
-      <c r="V8">
-        <v>-1</v>
-      </c>
-      <c r="W8">
-        <v>-1</v>
-      </c>
-      <c r="X8">
-        <v>-1</v>
-      </c>
-      <c r="Y8">
-        <v>-1</v>
-      </c>
-      <c r="Z8">
-        <v>5</v>
-      </c>
-      <c r="AA8">
-        <v>9</v>
-      </c>
-      <c r="AB8">
-        <v>6</v>
-      </c>
-      <c r="AC8">
-        <v>7</v>
-      </c>
-      <c r="AD8">
-        <v>5</v>
-      </c>
-      <c r="AE8">
-        <v>9</v>
-      </c>
-      <c r="AF8">
-        <v>5</v>
-      </c>
-      <c r="AG8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -1332,84 +1274,72 @@
         <v>9</v>
       </c>
       <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>9</v>
+      </c>
+      <c r="L9">
+        <v>9</v>
+      </c>
+      <c r="M9">
         <v>10</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>8</v>
-      </c>
-      <c r="L9">
-        <v>9</v>
-      </c>
-      <c r="M9">
-        <v>9</v>
       </c>
       <c r="N9">
         <v>10</v>
       </c>
       <c r="O9">
+        <v>8</v>
+      </c>
+      <c r="P9">
+        <v>-1</v>
+      </c>
+      <c r="Q9">
+        <v>-1</v>
+      </c>
+      <c r="R9">
+        <v>-1</v>
+      </c>
+      <c r="S9">
+        <v>-1</v>
+      </c>
+      <c r="T9">
+        <v>-1</v>
+      </c>
+      <c r="U9">
+        <v>-1</v>
+      </c>
+      <c r="V9">
+        <v>-1</v>
+      </c>
+      <c r="W9">
+        <v>8</v>
+      </c>
+      <c r="X9">
+        <v>9</v>
+      </c>
+      <c r="Y9">
+        <v>8</v>
+      </c>
+      <c r="Z9">
+        <v>9</v>
+      </c>
+      <c r="AA9">
         <v>10</v>
       </c>
-      <c r="P9">
-        <v>8</v>
-      </c>
-      <c r="Q9">
+      <c r="AB9">
         <v>10</v>
       </c>
-      <c r="R9">
-        <v>-1</v>
-      </c>
-      <c r="S9">
-        <v>-1</v>
-      </c>
-      <c r="T9">
-        <v>-1</v>
-      </c>
-      <c r="U9">
-        <v>-1</v>
-      </c>
-      <c r="V9">
-        <v>-1</v>
-      </c>
-      <c r="W9">
-        <v>-1</v>
-      </c>
-      <c r="X9">
-        <v>-1</v>
-      </c>
-      <c r="Y9">
-        <v>-1</v>
-      </c>
-      <c r="Z9">
-        <v>8</v>
-      </c>
-      <c r="AA9">
-        <v>9</v>
-      </c>
-      <c r="AB9">
-        <v>8</v>
-      </c>
       <c r="AC9">
         <v>9</v>
       </c>
-      <c r="AD9">
-        <v>10</v>
-      </c>
-      <c r="AE9">
-        <v>10</v>
-      </c>
-      <c r="AF9">
-        <v>9</v>
-      </c>
-      <c r="AG9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33">
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -1433,31 +1363,31 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1475,42 +1405,30 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>5</v>
-      </c>
-      <c r="AD10">
-        <v>7</v>
-      </c>
-      <c r="AE10">
-        <v>7</v>
-      </c>
-      <c r="AF10">
-        <v>6</v>
-      </c>
-      <c r="AG10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -1534,31 +1452,31 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1576,42 +1494,30 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC11">
-        <v>5</v>
-      </c>
-      <c r="AD11">
-        <v>5</v>
-      </c>
-      <c r="AE11">
-        <v>6</v>
-      </c>
-      <c r="AF11">
-        <v>6</v>
-      </c>
-      <c r="AG11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1635,31 +1541,31 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>7</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1677,13 +1583,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1692,27 +1598,15 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>5</v>
-      </c>
-      <c r="AD12">
-        <v>5</v>
-      </c>
-      <c r="AE12">
-        <v>6</v>
-      </c>
-      <c r="AF12">
-        <v>8</v>
-      </c>
-      <c r="AG12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -1736,31 +1630,31 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q13">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1778,42 +1672,30 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>5</v>
       </c>
-      <c r="AD13">
-        <v>5</v>
-      </c>
-      <c r="AE13">
-        <v>7</v>
-      </c>
-      <c r="AF13">
-        <v>5</v>
-      </c>
-      <c r="AG13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33">
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1837,31 +1719,31 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>6</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1879,143 +1761,119 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>5</v>
       </c>
-      <c r="AD14">
-        <v>9</v>
-      </c>
-      <c r="AE14">
-        <v>8</v>
-      </c>
-      <c r="AF14">
-        <v>5</v>
-      </c>
-      <c r="AG14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33">
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15">
+        <v>9</v>
+      </c>
+      <c r="O15">
+        <v>7</v>
+      </c>
+      <c r="P15">
+        <v>-1</v>
+      </c>
+      <c r="Q15">
+        <v>-1</v>
+      </c>
+      <c r="R15">
+        <v>-1</v>
+      </c>
+      <c r="S15">
+        <v>-1</v>
+      </c>
+      <c r="T15">
+        <v>-1</v>
+      </c>
+      <c r="U15">
+        <v>-1</v>
+      </c>
+      <c r="V15">
+        <v>-1</v>
+      </c>
+      <c r="W15">
+        <v>5</v>
+      </c>
+      <c r="X15">
+        <v>6</v>
+      </c>
+      <c r="Y15">
+        <v>7</v>
+      </c>
+      <c r="Z15">
+        <v>6</v>
+      </c>
+      <c r="AA15">
+        <v>5</v>
+      </c>
+      <c r="AB15">
+        <v>9</v>
+      </c>
+      <c r="AC15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-      <c r="D15">
-        <v>6</v>
-      </c>
-      <c r="E15">
-        <v>6</v>
-      </c>
-      <c r="F15">
-        <v>6</v>
-      </c>
-      <c r="G15">
-        <v>9</v>
-      </c>
-      <c r="H15">
-        <v>7</v>
-      </c>
-      <c r="I15">
-        <v>10</v>
-      </c>
-      <c r="J15">
-        <v>5</v>
-      </c>
-      <c r="K15">
-        <v>6</v>
-      </c>
-      <c r="L15">
-        <v>8</v>
-      </c>
-      <c r="M15">
-        <v>6</v>
-      </c>
-      <c r="N15">
-        <v>5</v>
-      </c>
-      <c r="O15">
-        <v>9</v>
-      </c>
-      <c r="P15">
-        <v>7</v>
-      </c>
-      <c r="Q15">
-        <v>10</v>
-      </c>
-      <c r="R15">
-        <v>-1</v>
-      </c>
-      <c r="S15">
-        <v>-1</v>
-      </c>
-      <c r="T15">
-        <v>-1</v>
-      </c>
-      <c r="U15">
-        <v>-1</v>
-      </c>
-      <c r="V15">
-        <v>-1</v>
-      </c>
-      <c r="W15">
-        <v>-1</v>
-      </c>
-      <c r="X15">
-        <v>-1</v>
-      </c>
-      <c r="Y15">
-        <v>-1</v>
-      </c>
-      <c r="Z15">
-        <v>5</v>
-      </c>
-      <c r="AA15">
-        <v>6</v>
-      </c>
-      <c r="AB15">
-        <v>7</v>
-      </c>
-      <c r="AC15">
-        <v>6</v>
-      </c>
-      <c r="AD15">
-        <v>5</v>
-      </c>
-      <c r="AE15">
-        <v>9</v>
-      </c>
-      <c r="AF15">
-        <v>7</v>
-      </c>
-      <c r="AG15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -2039,31 +1897,31 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2081,13 +1939,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -2101,22 +1959,10 @@
       <c r="AC16">
         <v>5</v>
       </c>
-      <c r="AD16">
-        <v>5</v>
-      </c>
-      <c r="AE16">
-        <v>5</v>
-      </c>
-      <c r="AF16">
-        <v>5</v>
-      </c>
-      <c r="AG16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33">
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2140,31 +1986,31 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q17">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2182,42 +2028,30 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>5</v>
-      </c>
-      <c r="AD17">
-        <v>8</v>
-      </c>
-      <c r="AE17">
-        <v>6</v>
-      </c>
-      <c r="AF17">
-        <v>7</v>
-      </c>
-      <c r="AG17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -2241,31 +2075,31 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>8</v>
       </c>
       <c r="O18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2283,42 +2117,30 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC18">
-        <v>5</v>
-      </c>
-      <c r="AD18">
-        <v>7</v>
-      </c>
-      <c r="AE18">
-        <v>9</v>
-      </c>
-      <c r="AF18">
-        <v>7</v>
-      </c>
-      <c r="AG18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -2342,31 +2164,31 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q19">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2384,42 +2206,30 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>5</v>
       </c>
-      <c r="AD19">
-        <v>6</v>
-      </c>
-      <c r="AE19">
-        <v>9</v>
-      </c>
-      <c r="AF19">
-        <v>5</v>
-      </c>
-      <c r="AG19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33">
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>8</v>
@@ -2443,286 +2253,250 @@
         <v>6</v>
       </c>
       <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>9</v>
+      </c>
+      <c r="K20">
+        <v>9</v>
+      </c>
+      <c r="L20">
         <v>10</v>
       </c>
-      <c r="J20">
-        <v>6</v>
-      </c>
-      <c r="K20">
-        <v>9</v>
-      </c>
-      <c r="L20">
-        <v>9</v>
-      </c>
       <c r="M20">
+        <v>7</v>
+      </c>
+      <c r="N20">
+        <v>9</v>
+      </c>
+      <c r="O20">
+        <v>6</v>
+      </c>
+      <c r="P20">
+        <v>-1</v>
+      </c>
+      <c r="Q20">
+        <v>-1</v>
+      </c>
+      <c r="R20">
+        <v>-1</v>
+      </c>
+      <c r="S20">
+        <v>-1</v>
+      </c>
+      <c r="T20">
+        <v>-1</v>
+      </c>
+      <c r="U20">
+        <v>-1</v>
+      </c>
+      <c r="V20">
+        <v>-1</v>
+      </c>
+      <c r="W20">
+        <v>7</v>
+      </c>
+      <c r="X20">
         <v>10</v>
       </c>
-      <c r="N20">
-        <v>7</v>
-      </c>
-      <c r="O20">
-        <v>9</v>
-      </c>
-      <c r="P20">
-        <v>6</v>
-      </c>
-      <c r="Q20">
+      <c r="Y20">
+        <v>8</v>
+      </c>
+      <c r="Z20">
+        <v>8</v>
+      </c>
+      <c r="AA20">
+        <v>8</v>
+      </c>
+      <c r="AB20">
+        <v>9</v>
+      </c>
+      <c r="AC20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="I21">
+        <v>6</v>
+      </c>
+      <c r="J21">
+        <v>8</v>
+      </c>
+      <c r="K21">
+        <v>8</v>
+      </c>
+      <c r="L21">
         <v>10</v>
       </c>
-      <c r="R20">
-        <v>-1</v>
-      </c>
-      <c r="S20">
-        <v>-1</v>
-      </c>
-      <c r="T20">
-        <v>-1</v>
-      </c>
-      <c r="U20">
-        <v>-1</v>
-      </c>
-      <c r="V20">
-        <v>-1</v>
-      </c>
-      <c r="W20">
-        <v>-1</v>
-      </c>
-      <c r="X20">
-        <v>-1</v>
-      </c>
-      <c r="Y20">
-        <v>-1</v>
-      </c>
-      <c r="Z20">
-        <v>7</v>
-      </c>
-      <c r="AA20">
-        <v>10</v>
-      </c>
-      <c r="AB20">
-        <v>8</v>
-      </c>
-      <c r="AC20">
-        <v>8</v>
-      </c>
-      <c r="AD20">
-        <v>8</v>
-      </c>
-      <c r="AE20">
-        <v>9</v>
-      </c>
-      <c r="AF20">
-        <v>6</v>
-      </c>
-      <c r="AG20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33">
-      <c r="A21" s="1" t="s">
+      <c r="M21">
+        <v>8</v>
+      </c>
+      <c r="N21">
+        <v>9</v>
+      </c>
+      <c r="O21">
+        <v>8</v>
+      </c>
+      <c r="P21">
+        <v>-1</v>
+      </c>
+      <c r="Q21">
+        <v>-1</v>
+      </c>
+      <c r="R21">
+        <v>-1</v>
+      </c>
+      <c r="S21">
+        <v>-1</v>
+      </c>
+      <c r="T21">
+        <v>-1</v>
+      </c>
+      <c r="U21">
+        <v>-1</v>
+      </c>
+      <c r="V21">
+        <v>-1</v>
+      </c>
+      <c r="W21">
+        <v>7</v>
+      </c>
+      <c r="X21">
+        <v>8</v>
+      </c>
+      <c r="Y21">
+        <v>8</v>
+      </c>
+      <c r="Z21">
+        <v>9</v>
+      </c>
+      <c r="AA21">
+        <v>9</v>
+      </c>
+      <c r="AB21">
+        <v>9</v>
+      </c>
+      <c r="AC21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21">
-        <v>8</v>
-      </c>
-      <c r="C21">
-        <v>8</v>
-      </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
-      <c r="E21">
-        <v>8</v>
-      </c>
-      <c r="F21">
-        <v>9</v>
-      </c>
-      <c r="G21">
-        <v>9</v>
-      </c>
-      <c r="H21">
-        <v>9</v>
-      </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
-        <v>6</v>
-      </c>
-      <c r="K21">
-        <v>8</v>
-      </c>
-      <c r="L21">
-        <v>8</v>
-      </c>
-      <c r="M21">
-        <v>10</v>
-      </c>
-      <c r="N21">
-        <v>8</v>
-      </c>
-      <c r="O21">
-        <v>9</v>
-      </c>
-      <c r="P21">
-        <v>8</v>
-      </c>
-      <c r="Q21">
-        <v>10</v>
-      </c>
-      <c r="R21">
-        <v>-1</v>
-      </c>
-      <c r="S21">
-        <v>-1</v>
-      </c>
-      <c r="T21">
-        <v>-1</v>
-      </c>
-      <c r="U21">
-        <v>-1</v>
-      </c>
-      <c r="V21">
-        <v>-1</v>
-      </c>
-      <c r="W21">
-        <v>-1</v>
-      </c>
-      <c r="X21">
-        <v>-1</v>
-      </c>
-      <c r="Y21">
-        <v>-1</v>
-      </c>
-      <c r="Z21">
-        <v>7</v>
-      </c>
-      <c r="AA21">
-        <v>8</v>
-      </c>
-      <c r="AB21">
-        <v>8</v>
-      </c>
-      <c r="AC21">
-        <v>9</v>
-      </c>
-      <c r="AD21">
-        <v>9</v>
-      </c>
-      <c r="AE21">
-        <v>9</v>
-      </c>
-      <c r="AF21">
-        <v>9</v>
-      </c>
-      <c r="AG21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33">
-      <c r="A22" s="1" t="s">
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>9</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <v>7</v>
+      </c>
+      <c r="L22">
+        <v>8</v>
+      </c>
+      <c r="M22">
+        <v>6</v>
+      </c>
+      <c r="N22">
+        <v>9</v>
+      </c>
+      <c r="O22">
+        <v>8</v>
+      </c>
+      <c r="P22">
+        <v>-1</v>
+      </c>
+      <c r="Q22">
+        <v>-1</v>
+      </c>
+      <c r="R22">
+        <v>-1</v>
+      </c>
+      <c r="S22">
+        <v>-1</v>
+      </c>
+      <c r="T22">
+        <v>-1</v>
+      </c>
+      <c r="U22">
+        <v>-1</v>
+      </c>
+      <c r="V22">
+        <v>-1</v>
+      </c>
+      <c r="W22">
+        <v>5</v>
+      </c>
+      <c r="X22">
+        <v>6</v>
+      </c>
+      <c r="Y22">
+        <v>7</v>
+      </c>
+      <c r="Z22">
+        <v>7</v>
+      </c>
+      <c r="AA22">
+        <v>8</v>
+      </c>
+      <c r="AB22">
+        <v>9</v>
+      </c>
+      <c r="AC22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
+      <c r="A23" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B22">
-        <v>6</v>
-      </c>
-      <c r="C22">
-        <v>5</v>
-      </c>
-      <c r="D22">
-        <v>7</v>
-      </c>
-      <c r="E22">
-        <v>6</v>
-      </c>
-      <c r="F22">
-        <v>9</v>
-      </c>
-      <c r="G22">
-        <v>9</v>
-      </c>
-      <c r="H22">
-        <v>7</v>
-      </c>
-      <c r="I22">
-        <v>10</v>
-      </c>
-      <c r="J22">
-        <v>5</v>
-      </c>
-      <c r="K22">
-        <v>7</v>
-      </c>
-      <c r="L22">
-        <v>7</v>
-      </c>
-      <c r="M22">
-        <v>8</v>
-      </c>
-      <c r="N22">
-        <v>6</v>
-      </c>
-      <c r="O22">
-        <v>9</v>
-      </c>
-      <c r="P22">
-        <v>8</v>
-      </c>
-      <c r="Q22">
-        <v>5</v>
-      </c>
-      <c r="R22">
-        <v>-1</v>
-      </c>
-      <c r="S22">
-        <v>-1</v>
-      </c>
-      <c r="T22">
-        <v>-1</v>
-      </c>
-      <c r="U22">
-        <v>-1</v>
-      </c>
-      <c r="V22">
-        <v>-1</v>
-      </c>
-      <c r="W22">
-        <v>-1</v>
-      </c>
-      <c r="X22">
-        <v>-1</v>
-      </c>
-      <c r="Y22">
-        <v>-1</v>
-      </c>
-      <c r="Z22">
-        <v>5</v>
-      </c>
-      <c r="AA22">
-        <v>6</v>
-      </c>
-      <c r="AB22">
-        <v>7</v>
-      </c>
-      <c r="AC22">
-        <v>7</v>
-      </c>
-      <c r="AD22">
-        <v>8</v>
-      </c>
-      <c r="AE22">
-        <v>9</v>
-      </c>
-      <c r="AF22">
-        <v>8</v>
-      </c>
-      <c r="AG22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33">
-      <c r="A23" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="B23">
         <v>7</v>
@@ -2746,84 +2520,72 @@
         <v>10</v>
       </c>
       <c r="I23">
+        <v>9</v>
+      </c>
+      <c r="J23">
+        <v>8</v>
+      </c>
+      <c r="K23">
+        <v>9</v>
+      </c>
+      <c r="L23">
         <v>10</v>
-      </c>
-      <c r="J23">
-        <v>9</v>
-      </c>
-      <c r="K23">
-        <v>8</v>
-      </c>
-      <c r="L23">
-        <v>9</v>
       </c>
       <c r="M23">
         <v>10</v>
       </c>
       <c r="N23">
+        <v>9</v>
+      </c>
+      <c r="O23">
+        <v>9</v>
+      </c>
+      <c r="P23">
+        <v>-1</v>
+      </c>
+      <c r="Q23">
+        <v>-1</v>
+      </c>
+      <c r="R23">
+        <v>-1</v>
+      </c>
+      <c r="S23">
+        <v>-1</v>
+      </c>
+      <c r="T23">
+        <v>-1</v>
+      </c>
+      <c r="U23">
+        <v>-1</v>
+      </c>
+      <c r="V23">
+        <v>-1</v>
+      </c>
+      <c r="W23">
+        <v>8</v>
+      </c>
+      <c r="X23">
+        <v>9</v>
+      </c>
+      <c r="Y23">
+        <v>8</v>
+      </c>
+      <c r="Z23">
         <v>10</v>
       </c>
-      <c r="O23">
-        <v>9</v>
-      </c>
-      <c r="P23">
-        <v>9</v>
-      </c>
-      <c r="Q23">
+      <c r="AA23">
         <v>10</v>
       </c>
-      <c r="R23">
-        <v>-1</v>
-      </c>
-      <c r="S23">
-        <v>-1</v>
-      </c>
-      <c r="T23">
-        <v>-1</v>
-      </c>
-      <c r="U23">
-        <v>-1</v>
-      </c>
-      <c r="V23">
-        <v>-1</v>
-      </c>
-      <c r="W23">
-        <v>-1</v>
-      </c>
-      <c r="X23">
-        <v>-1</v>
-      </c>
-      <c r="Y23">
-        <v>-1</v>
-      </c>
-      <c r="Z23">
-        <v>8</v>
-      </c>
-      <c r="AA23">
-        <v>9</v>
-      </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>10</v>
       </c>
-      <c r="AD23">
-        <v>10</v>
-      </c>
-      <c r="AE23">
-        <v>9</v>
-      </c>
-      <c r="AF23">
-        <v>10</v>
-      </c>
-      <c r="AG23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33">
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2847,31 +2609,31 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2889,42 +2651,30 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>5</v>
       </c>
-      <c r="AD24">
-        <v>5</v>
-      </c>
-      <c r="AE24">
-        <v>7</v>
-      </c>
-      <c r="AF24">
-        <v>5</v>
-      </c>
-      <c r="AG24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33">
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -2948,31 +2698,31 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>5</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q25">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2990,42 +2740,30 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC25">
-        <v>5</v>
-      </c>
-      <c r="AD25">
-        <v>5</v>
-      </c>
-      <c r="AE25">
-        <v>9</v>
-      </c>
-      <c r="AF25">
-        <v>7</v>
-      </c>
-      <c r="AG25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -3049,31 +2787,31 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>7</v>
       </c>
       <c r="P26">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q26">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3091,42 +2829,30 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>5</v>
-      </c>
-      <c r="AD26">
-        <v>5</v>
-      </c>
-      <c r="AE26">
-        <v>8</v>
-      </c>
-      <c r="AF26">
-        <v>7</v>
-      </c>
-      <c r="AG26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -3150,31 +2876,31 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>6</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q27">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3192,42 +2918,30 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC27">
-        <v>7</v>
-      </c>
-      <c r="AD27">
-        <v>8</v>
-      </c>
-      <c r="AE27">
-        <v>6</v>
-      </c>
-      <c r="AF27">
-        <v>8</v>
-      </c>
-      <c r="AG27">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -3251,31 +2965,31 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Q28">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3293,13 +3007,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>5</v>
@@ -3311,125 +3025,101 @@
         <v>6</v>
       </c>
       <c r="AC28">
-        <v>5</v>
-      </c>
-      <c r="AD28">
-        <v>8</v>
-      </c>
-      <c r="AE28">
-        <v>6</v>
-      </c>
-      <c r="AF28">
-        <v>8</v>
-      </c>
-      <c r="AG28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>6</v>
+      </c>
+      <c r="K29">
+        <v>6</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
+      </c>
+      <c r="N29">
+        <v>7</v>
+      </c>
+      <c r="O29">
+        <v>7</v>
+      </c>
+      <c r="P29">
+        <v>-1</v>
+      </c>
+      <c r="Q29">
+        <v>-1</v>
+      </c>
+      <c r="R29">
+        <v>-1</v>
+      </c>
+      <c r="S29">
+        <v>-1</v>
+      </c>
+      <c r="T29">
+        <v>-1</v>
+      </c>
+      <c r="U29">
+        <v>-1</v>
+      </c>
+      <c r="V29">
+        <v>-1</v>
+      </c>
+      <c r="W29">
+        <v>5</v>
+      </c>
+      <c r="X29">
+        <v>6</v>
+      </c>
+      <c r="Y29">
+        <v>6</v>
+      </c>
+      <c r="Z29">
+        <v>5</v>
+      </c>
+      <c r="AA29">
+        <v>6</v>
+      </c>
+      <c r="AB29">
+        <v>8</v>
+      </c>
+      <c r="AC29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B29">
-        <v>6</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
-      <c r="D29">
-        <v>6</v>
-      </c>
-      <c r="E29">
-        <v>6</v>
-      </c>
-      <c r="F29">
-        <v>7</v>
-      </c>
-      <c r="G29">
-        <v>8</v>
-      </c>
-      <c r="H29">
-        <v>7</v>
-      </c>
-      <c r="I29">
-        <v>10</v>
-      </c>
-      <c r="J29">
-        <v>5</v>
-      </c>
-      <c r="K29">
-        <v>6</v>
-      </c>
-      <c r="L29">
-        <v>6</v>
-      </c>
-      <c r="M29">
-        <v>5</v>
-      </c>
-      <c r="N29">
-        <v>5</v>
-      </c>
-      <c r="O29">
-        <v>7</v>
-      </c>
-      <c r="P29">
-        <v>7</v>
-      </c>
-      <c r="Q29">
-        <v>10</v>
-      </c>
-      <c r="R29">
-        <v>-1</v>
-      </c>
-      <c r="S29">
-        <v>-1</v>
-      </c>
-      <c r="T29">
-        <v>-1</v>
-      </c>
-      <c r="U29">
-        <v>-1</v>
-      </c>
-      <c r="V29">
-        <v>-1</v>
-      </c>
-      <c r="W29">
-        <v>-1</v>
-      </c>
-      <c r="X29">
-        <v>-1</v>
-      </c>
-      <c r="Y29">
-        <v>-1</v>
-      </c>
-      <c r="Z29">
-        <v>5</v>
-      </c>
-      <c r="AA29">
-        <v>6</v>
-      </c>
-      <c r="AB29">
-        <v>6</v>
-      </c>
-      <c r="AC29">
-        <v>5</v>
-      </c>
-      <c r="AD29">
-        <v>6</v>
-      </c>
-      <c r="AE29">
-        <v>8</v>
-      </c>
-      <c r="AF29">
-        <v>7</v>
-      </c>
-      <c r="AG29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33">
-      <c r="A30" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -3453,31 +3143,31 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q30">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3495,143 +3185,119 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>7</v>
       </c>
-      <c r="AD30">
-        <v>5</v>
-      </c>
-      <c r="AE30">
-        <v>9</v>
-      </c>
-      <c r="AF30">
-        <v>7</v>
-      </c>
-      <c r="AG30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33">
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>5</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>7</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31">
+        <v>9</v>
+      </c>
+      <c r="K31">
+        <v>5</v>
+      </c>
+      <c r="L31">
+        <v>5</v>
+      </c>
+      <c r="M31">
+        <v>5</v>
+      </c>
+      <c r="N31">
+        <v>7</v>
+      </c>
+      <c r="O31">
+        <v>6</v>
+      </c>
+      <c r="P31">
+        <v>-1</v>
+      </c>
+      <c r="Q31">
+        <v>-1</v>
+      </c>
+      <c r="R31">
+        <v>-1</v>
+      </c>
+      <c r="S31">
+        <v>-1</v>
+      </c>
+      <c r="T31">
+        <v>-1</v>
+      </c>
+      <c r="U31">
+        <v>-1</v>
+      </c>
+      <c r="V31">
+        <v>-1</v>
+      </c>
+      <c r="W31">
+        <v>5</v>
+      </c>
+      <c r="X31">
+        <v>7</v>
+      </c>
+      <c r="Y31">
+        <v>5</v>
+      </c>
+      <c r="Z31">
+        <v>5</v>
+      </c>
+      <c r="AA31">
+        <v>5</v>
+      </c>
+      <c r="AB31">
+        <v>8</v>
+      </c>
+      <c r="AC31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>5</v>
-      </c>
-      <c r="D31">
-        <v>6</v>
-      </c>
-      <c r="E31">
-        <v>5</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31">
-        <v>8</v>
-      </c>
-      <c r="H31">
-        <v>7</v>
-      </c>
-      <c r="I31">
-        <v>10</v>
-      </c>
-      <c r="J31">
-        <v>5</v>
-      </c>
-      <c r="K31">
-        <v>9</v>
-      </c>
-      <c r="L31">
-        <v>5</v>
-      </c>
-      <c r="M31">
-        <v>5</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>7</v>
-      </c>
-      <c r="P31">
-        <v>6</v>
-      </c>
-      <c r="Q31">
-        <v>10</v>
-      </c>
-      <c r="R31">
-        <v>-1</v>
-      </c>
-      <c r="S31">
-        <v>-1</v>
-      </c>
-      <c r="T31">
-        <v>-1</v>
-      </c>
-      <c r="U31">
-        <v>-1</v>
-      </c>
-      <c r="V31">
-        <v>-1</v>
-      </c>
-      <c r="W31">
-        <v>-1</v>
-      </c>
-      <c r="X31">
-        <v>-1</v>
-      </c>
-      <c r="Y31">
-        <v>-1</v>
-      </c>
-      <c r="Z31">
-        <v>5</v>
-      </c>
-      <c r="AA31">
-        <v>7</v>
-      </c>
-      <c r="AB31">
-        <v>5</v>
-      </c>
-      <c r="AC31">
-        <v>5</v>
-      </c>
-      <c r="AD31">
-        <v>5</v>
-      </c>
-      <c r="AE31">
-        <v>8</v>
-      </c>
-      <c r="AF31">
-        <v>7</v>
-      </c>
-      <c r="AG31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33">
-      <c r="A32" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="B32">
         <v>5</v>
@@ -3655,31 +3321,31 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>5</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q32">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3697,13 +3363,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3717,22 +3383,10 @@
       <c r="AC32">
         <v>5</v>
       </c>
-      <c r="AD32">
-        <v>5</v>
-      </c>
-      <c r="AE32">
-        <v>5</v>
-      </c>
-      <c r="AF32">
-        <v>5</v>
-      </c>
-      <c r="AG32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:33">
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>6</v>
@@ -3756,84 +3410,72 @@
         <v>10</v>
       </c>
       <c r="I33">
+        <v>8</v>
+      </c>
+      <c r="J33">
+        <v>9</v>
+      </c>
+      <c r="K33">
+        <v>7</v>
+      </c>
+      <c r="L33">
+        <v>9</v>
+      </c>
+      <c r="M33">
         <v>10</v>
       </c>
-      <c r="J33">
-        <v>8</v>
-      </c>
-      <c r="K33">
-        <v>9</v>
-      </c>
-      <c r="L33">
-        <v>7</v>
-      </c>
-      <c r="M33">
-        <v>9</v>
-      </c>
       <c r="N33">
+        <v>9</v>
+      </c>
+      <c r="O33">
         <v>10</v>
       </c>
-      <c r="O33">
-        <v>9</v>
-      </c>
       <c r="P33">
+        <v>-1</v>
+      </c>
+      <c r="Q33">
+        <v>-1</v>
+      </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>-1</v>
+      </c>
+      <c r="U33">
+        <v>-1</v>
+      </c>
+      <c r="V33">
+        <v>-1</v>
+      </c>
+      <c r="W33">
+        <v>7</v>
+      </c>
+      <c r="X33">
+        <v>9</v>
+      </c>
+      <c r="Y33">
+        <v>7</v>
+      </c>
+      <c r="Z33">
+        <v>7</v>
+      </c>
+      <c r="AA33">
         <v>10</v>
       </c>
-      <c r="Q33">
+      <c r="AB33">
+        <v>8</v>
+      </c>
+      <c r="AC33">
         <v>10</v>
       </c>
-      <c r="R33">
-        <v>-1</v>
-      </c>
-      <c r="S33">
-        <v>-1</v>
-      </c>
-      <c r="T33">
-        <v>-1</v>
-      </c>
-      <c r="U33">
-        <v>-1</v>
-      </c>
-      <c r="V33">
-        <v>-1</v>
-      </c>
-      <c r="W33">
-        <v>-1</v>
-      </c>
-      <c r="X33">
-        <v>-1</v>
-      </c>
-      <c r="Y33">
-        <v>-1</v>
-      </c>
-      <c r="Z33">
-        <v>7</v>
-      </c>
-      <c r="AA33">
-        <v>9</v>
-      </c>
-      <c r="AB33">
-        <v>7</v>
-      </c>
-      <c r="AC33">
-        <v>7</v>
-      </c>
-      <c r="AD33">
-        <v>10</v>
-      </c>
-      <c r="AE33">
-        <v>8</v>
-      </c>
-      <c r="AF33">
-        <v>10</v>
-      </c>
-      <c r="AG33">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33">
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3857,16 +3499,16 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>5</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3878,10 +3520,10 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3899,13 +3541,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z34">
         <v>5</v>
@@ -3919,22 +3561,10 @@
       <c r="AC34">
         <v>5</v>
       </c>
-      <c r="AD34">
-        <v>5</v>
-      </c>
-      <c r="AE34">
-        <v>5</v>
-      </c>
-      <c r="AF34">
-        <v>5</v>
-      </c>
-      <c r="AG34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33">
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -3958,31 +3588,31 @@
         <v>5</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q35">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4000,143 +3630,119 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC35">
         <v>5</v>
       </c>
-      <c r="AD35">
-        <v>6</v>
-      </c>
-      <c r="AE35">
-        <v>7</v>
-      </c>
-      <c r="AF35">
-        <v>5</v>
-      </c>
-      <c r="AG35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33">
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>6</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>8</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>8</v>
+      </c>
+      <c r="J36">
+        <v>7</v>
+      </c>
+      <c r="K36">
+        <v>6</v>
+      </c>
+      <c r="L36">
+        <v>7</v>
+      </c>
+      <c r="M36">
+        <v>5</v>
+      </c>
+      <c r="N36">
+        <v>9</v>
+      </c>
+      <c r="O36">
+        <v>7</v>
+      </c>
+      <c r="P36">
+        <v>-1</v>
+      </c>
+      <c r="Q36">
+        <v>-1</v>
+      </c>
+      <c r="R36">
+        <v>-1</v>
+      </c>
+      <c r="S36">
+        <v>-1</v>
+      </c>
+      <c r="T36">
+        <v>-1</v>
+      </c>
+      <c r="U36">
+        <v>-1</v>
+      </c>
+      <c r="V36">
+        <v>-1</v>
+      </c>
+      <c r="W36">
+        <v>7</v>
+      </c>
+      <c r="X36">
+        <v>8</v>
+      </c>
+      <c r="Y36">
+        <v>6</v>
+      </c>
+      <c r="Z36">
+        <v>7</v>
+      </c>
+      <c r="AA36">
+        <v>6</v>
+      </c>
+      <c r="AB36">
+        <v>9</v>
+      </c>
+      <c r="AC36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
+      <c r="A37" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B36">
-        <v>6</v>
-      </c>
-      <c r="C36">
-        <v>9</v>
-      </c>
-      <c r="D36">
-        <v>6</v>
-      </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
-      <c r="F36">
-        <v>7</v>
-      </c>
-      <c r="G36">
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>5</v>
-      </c>
-      <c r="I36">
-        <v>10</v>
-      </c>
-      <c r="J36">
-        <v>8</v>
-      </c>
-      <c r="K36">
-        <v>7</v>
-      </c>
-      <c r="L36">
-        <v>6</v>
-      </c>
-      <c r="M36">
-        <v>7</v>
-      </c>
-      <c r="N36">
-        <v>5</v>
-      </c>
-      <c r="O36">
-        <v>9</v>
-      </c>
-      <c r="P36">
-        <v>7</v>
-      </c>
-      <c r="Q36">
-        <v>10</v>
-      </c>
-      <c r="R36">
-        <v>-1</v>
-      </c>
-      <c r="S36">
-        <v>-1</v>
-      </c>
-      <c r="T36">
-        <v>-1</v>
-      </c>
-      <c r="U36">
-        <v>-1</v>
-      </c>
-      <c r="V36">
-        <v>-1</v>
-      </c>
-      <c r="W36">
-        <v>-1</v>
-      </c>
-      <c r="X36">
-        <v>-1</v>
-      </c>
-      <c r="Y36">
-        <v>-1</v>
-      </c>
-      <c r="Z36">
-        <v>7</v>
-      </c>
-      <c r="AA36">
-        <v>8</v>
-      </c>
-      <c r="AB36">
-        <v>6</v>
-      </c>
-      <c r="AC36">
-        <v>7</v>
-      </c>
-      <c r="AD36">
-        <v>6</v>
-      </c>
-      <c r="AE36">
-        <v>9</v>
-      </c>
-      <c r="AF36">
-        <v>6</v>
-      </c>
-      <c r="AG36">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:33">
-      <c r="A37" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -4160,31 +3766,31 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>5</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q37">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4202,45 +3808,33 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>5</v>
-      </c>
-      <c r="AD37">
-        <v>5</v>
-      </c>
-      <c r="AE37">
-        <v>8</v>
-      </c>
-      <c r="AF37">
-        <v>5</v>
-      </c>
-      <c r="AG37">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="R1:Y1"/>
-    <mergeCell ref="Z1:AG1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="W1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4248,16 +3842,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4265,29 +3859,26 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25">
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4313,65 +3904,56 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="B4">
         <v>90</v>
@@ -4395,60 +3977,51 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L4">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="M4">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
         <v>90</v>
       </c>
-      <c r="K4">
-        <v>100</v>
-      </c>
-      <c r="L4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>84.09999999999999</v>
       </c>
-      <c r="M4">
+      <c r="S4">
         <v>96.90000000000001</v>
       </c>
-      <c r="N4">
+      <c r="T4">
         <v>97.59999999999999</v>
       </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
-        <v>100</v>
-      </c>
-      <c r="Q4">
-        <v>90</v>
-      </c>
-      <c r="R4">
-        <v>90</v>
-      </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>84.09999999999999</v>
-      </c>
       <c r="U4">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="W4">
-        <v>100</v>
-      </c>
-      <c r="X4">
-        <v>100</v>
-      </c>
-      <c r="Y4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>90</v>
@@ -4472,34 +4045,34 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
         <v>95</v>
       </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4513,19 +4086,10 @@
       <c r="V5">
         <v>100</v>
       </c>
-      <c r="W5">
-        <v>100</v>
-      </c>
-      <c r="X5">
-        <v>100</v>
-      </c>
-      <c r="Y5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>70</v>
@@ -4549,40 +4113,40 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>75</v>
       </c>
-      <c r="K6">
-        <v>100</v>
-      </c>
-      <c r="L6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>90.90000000000001</v>
       </c>
-      <c r="M6">
-        <v>100</v>
-      </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
-      <c r="Q6">
-        <v>90</v>
-      </c>
-      <c r="R6">
-        <v>75</v>
-      </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4590,96 +4154,78 @@
       <c r="V6">
         <v>100</v>
       </c>
-      <c r="W6">
-        <v>100</v>
-      </c>
-      <c r="X6">
-        <v>100</v>
-      </c>
-      <c r="Y6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>97.7</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>97.7</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="L7">
-        <v>97.7</v>
-      </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <v>90</v>
-      </c>
-      <c r="R7">
-        <v>100</v>
-      </c>
-      <c r="S7">
-        <v>100</v>
-      </c>
-      <c r="T7">
-        <v>97.7</v>
-      </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
-      <c r="V7">
-        <v>100</v>
-      </c>
-      <c r="W7">
-        <v>100</v>
-      </c>
-      <c r="X7">
-        <v>100</v>
-      </c>
-      <c r="Y7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="B8">
         <v>60</v>
@@ -4703,137 +4249,119 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
         <v>65</v>
       </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="L8">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>88.59999999999999</v>
       </c>
-      <c r="M8">
-        <v>100</v>
-      </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
         <v>96.90000000000001</v>
       </c>
-      <c r="P8">
-        <v>100</v>
-      </c>
-      <c r="Q8">
-        <v>80</v>
-      </c>
-      <c r="R8">
-        <v>65</v>
-      </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="U8">
-        <v>100</v>
-      </c>
       <c r="V8">
         <v>100</v>
       </c>
-      <c r="W8">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X8">
-        <v>100</v>
-      </c>
-      <c r="Y8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>95</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>95</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9">
-        <v>95</v>
-      </c>
-      <c r="K9">
-        <v>100</v>
-      </c>
-      <c r="L9">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="M9">
-        <v>100</v>
-      </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
-      <c r="Q9">
-        <v>90</v>
-      </c>
-      <c r="R9">
-        <v>95</v>
-      </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="U9">
-        <v>100</v>
-      </c>
-      <c r="V9">
-        <v>100</v>
-      </c>
-      <c r="W9">
-        <v>100</v>
-      </c>
-      <c r="X9">
-        <v>100</v>
-      </c>
-      <c r="Y9">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="B10">
         <v>90</v>
@@ -4857,40 +4385,40 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L10">
+        <v>93.8</v>
+      </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <v>93.8</v>
+      </c>
+      <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
         <v>80</v>
       </c>
-      <c r="K10">
-        <v>100</v>
-      </c>
-      <c r="L10">
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>88.59999999999999</v>
       </c>
-      <c r="M10">
+      <c r="S10">
         <v>93.8</v>
       </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10">
-        <v>93.8</v>
-      </c>
-      <c r="P10">
-        <v>100</v>
-      </c>
-      <c r="Q10">
-        <v>80</v>
-      </c>
-      <c r="R10">
-        <v>80</v>
-      </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
       <c r="T10">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="U10">
         <v>93.8</v>
@@ -4898,19 +4426,10 @@
       <c r="V10">
         <v>100</v>
       </c>
-      <c r="W10">
-        <v>93.8</v>
-      </c>
-      <c r="X10">
-        <v>100</v>
-      </c>
-      <c r="Y10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -4934,60 +4453,51 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L11">
+        <v>93.8</v>
+      </c>
+      <c r="M11">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="N11">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>75</v>
       </c>
-      <c r="K11">
-        <v>100</v>
-      </c>
-      <c r="L11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>84.09999999999999</v>
       </c>
-      <c r="M11">
+      <c r="S11">
         <v>93.8</v>
       </c>
-      <c r="N11">
+      <c r="T11">
         <v>97.59999999999999</v>
       </c>
-      <c r="O11">
+      <c r="U11">
         <v>96.90000000000001</v>
       </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-      <c r="Q11">
-        <v>80</v>
-      </c>
-      <c r="R11">
-        <v>75</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="U11">
-        <v>93.8</v>
-      </c>
       <c r="V11">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="W11">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X11">
-        <v>100</v>
-      </c>
-      <c r="Y11">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>70</v>
@@ -5011,60 +4521,51 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>77.3</v>
+      </c>
+      <c r="L12">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="M12">
+        <v>95.2</v>
+      </c>
+      <c r="N12">
+        <v>93.8</v>
+      </c>
+      <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
         <v>55</v>
       </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
-      <c r="L12">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>77.3</v>
       </c>
-      <c r="M12">
+      <c r="S12">
         <v>84.40000000000001</v>
       </c>
-      <c r="N12">
+      <c r="T12">
         <v>95.2</v>
       </c>
-      <c r="O12">
+      <c r="U12">
         <v>93.8</v>
       </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
-      <c r="Q12">
-        <v>80</v>
-      </c>
-      <c r="R12">
-        <v>55</v>
-      </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>77.3</v>
-      </c>
-      <c r="U12">
-        <v>84.40000000000001</v>
-      </c>
       <c r="V12">
-        <v>95.2</v>
-      </c>
-      <c r="W12">
-        <v>93.8</v>
-      </c>
-      <c r="X12">
-        <v>100</v>
-      </c>
-      <c r="Y12">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>60</v>
@@ -5088,60 +4589,51 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>79.5</v>
+      </c>
+      <c r="L13">
+        <v>93.8</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>80</v>
       </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>79.5</v>
       </c>
-      <c r="M13">
+      <c r="S13">
         <v>93.8</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
         <v>96.90000000000001</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>90</v>
-      </c>
-      <c r="R13">
-        <v>80</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
-        <v>79.5</v>
-      </c>
-      <c r="U13">
-        <v>93.8</v>
-      </c>
       <c r="V13">
         <v>100</v>
       </c>
-      <c r="W13">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X13">
-        <v>100</v>
-      </c>
-      <c r="Y13">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>90</v>
@@ -5165,40 +4657,40 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
         <v>80</v>
       </c>
-      <c r="K14">
-        <v>100</v>
-      </c>
-      <c r="L14">
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>90.90000000000001</v>
       </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
-      <c r="Q14">
-        <v>80</v>
-      </c>
-      <c r="R14">
-        <v>80</v>
-      </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -5206,19 +4698,10 @@
       <c r="V14">
         <v>100</v>
       </c>
-      <c r="W14">
-        <v>100</v>
-      </c>
-      <c r="X14">
-        <v>100</v>
-      </c>
-      <c r="Y14">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>90</v>
@@ -5242,60 +4725,51 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>93.2</v>
+      </c>
+      <c r="L15">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M15">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
         <v>75</v>
       </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>93.2</v>
       </c>
-      <c r="M15">
+      <c r="S15">
         <v>90.59999999999999</v>
       </c>
-      <c r="N15">
+      <c r="T15">
         <v>97.59999999999999</v>
       </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>75</v>
-      </c>
-      <c r="S15">
-        <v>100</v>
-      </c>
-      <c r="T15">
-        <v>93.2</v>
-      </c>
       <c r="U15">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="W15">
-        <v>100</v>
-      </c>
-      <c r="X15">
-        <v>100</v>
-      </c>
-      <c r="Y15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -5325,54 +4799,45 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>76.2</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>90.90000000000001</v>
       </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>76.2</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>100</v>
-      </c>
-      <c r="Q16">
-        <v>80</v>
-      </c>
-      <c r="R16">
-        <v>100</v>
-      </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
-        <v>90.90000000000001</v>
-      </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>76.2</v>
-      </c>
-      <c r="W16">
-        <v>100</v>
-      </c>
-      <c r="X16">
-        <v>100</v>
-      </c>
-      <c r="Y16">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -5396,60 +4861,51 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L17">
+        <v>81.3</v>
+      </c>
+      <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
+        <v>93.8</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>80</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>84.09999999999999</v>
       </c>
-      <c r="M17">
+      <c r="S17">
         <v>81.3</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
         <v>93.8</v>
       </c>
-      <c r="P17">
-        <v>100</v>
-      </c>
-      <c r="Q17">
-        <v>80</v>
-      </c>
-      <c r="R17">
-        <v>80</v>
-      </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="U17">
-        <v>81.3</v>
-      </c>
       <c r="V17">
         <v>100</v>
       </c>
-      <c r="W17">
-        <v>93.8</v>
-      </c>
-      <c r="X17">
-        <v>100</v>
-      </c>
-      <c r="Y17">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>70</v>
@@ -5473,60 +4929,51 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>81.8</v>
+      </c>
+      <c r="L18">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M18">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>70</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>81.8</v>
       </c>
-      <c r="M18">
+      <c r="S18">
         <v>90.59999999999999</v>
       </c>
-      <c r="N18">
+      <c r="T18">
         <v>97.59999999999999</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
-      <c r="P18">
-        <v>100</v>
-      </c>
-      <c r="Q18">
-        <v>80</v>
-      </c>
-      <c r="R18">
-        <v>70</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
-        <v>81.8</v>
-      </c>
       <c r="U18">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="W18">
-        <v>100</v>
-      </c>
-      <c r="X18">
-        <v>100</v>
-      </c>
-      <c r="Y18">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -5550,60 +4997,51 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>81.8</v>
+      </c>
+      <c r="L19">
+        <v>87.5</v>
+      </c>
+      <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>90</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>81.8</v>
       </c>
-      <c r="M19">
+      <c r="S19">
         <v>87.5</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19">
+      <c r="T19">
+        <v>100</v>
+      </c>
+      <c r="U19">
         <v>84.40000000000001</v>
       </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
-        <v>90</v>
-      </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
-        <v>81.8</v>
-      </c>
-      <c r="U19">
-        <v>87.5</v>
-      </c>
       <c r="V19">
         <v>100</v>
       </c>
-      <c r="W19">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="X19">
-        <v>100</v>
-      </c>
-      <c r="Y19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>80</v>
@@ -5627,214 +5065,187 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L20">
+        <v>100</v>
+      </c>
+      <c r="M20">
+        <v>100</v>
+      </c>
+      <c r="N20">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
         <v>90</v>
       </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>90.90000000000001</v>
       </c>
-      <c r="M20">
-        <v>100</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20">
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20">
         <v>96.90000000000001</v>
       </c>
-      <c r="P20">
-        <v>100</v>
-      </c>
-      <c r="Q20">
-        <v>90</v>
-      </c>
-      <c r="R20">
-        <v>90</v>
-      </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
-      <c r="T20">
+      <c r="V20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>100</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>100</v>
+      </c>
+      <c r="V21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>100</v>
+      </c>
+      <c r="E22">
+        <v>100</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
+        <v>100</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>90.90000000000001</v>
       </c>
-      <c r="U20">
-        <v>100</v>
-      </c>
-      <c r="V20">
-        <v>100</v>
-      </c>
-      <c r="W20">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X20">
-        <v>100</v>
-      </c>
-      <c r="Y20">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21">
-        <v>100</v>
-      </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-      <c r="D21">
-        <v>100</v>
-      </c>
-      <c r="E21">
-        <v>100</v>
-      </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>100</v>
-      </c>
-      <c r="H21">
-        <v>100</v>
-      </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
-      <c r="Q21">
-        <v>90</v>
-      </c>
-      <c r="R21">
-        <v>100</v>
-      </c>
-      <c r="S21">
-        <v>100</v>
-      </c>
-      <c r="T21">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="U21">
-        <v>100</v>
-      </c>
-      <c r="V21">
-        <v>100</v>
-      </c>
-      <c r="W21">
-        <v>100</v>
-      </c>
-      <c r="X21">
-        <v>100</v>
-      </c>
-      <c r="Y21">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
+        <v>100</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B22">
-        <v>100</v>
-      </c>
-      <c r="C22">
-        <v>100</v>
-      </c>
-      <c r="D22">
-        <v>100</v>
-      </c>
-      <c r="E22">
-        <v>100</v>
-      </c>
-      <c r="F22">
-        <v>100</v>
-      </c>
-      <c r="G22">
-        <v>100</v>
-      </c>
-      <c r="H22">
-        <v>100</v>
-      </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
-      <c r="P22">
-        <v>100</v>
-      </c>
-      <c r="Q22">
-        <v>80</v>
-      </c>
-      <c r="R22">
-        <v>100</v>
-      </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="U22">
-        <v>100</v>
-      </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-      <c r="W22">
-        <v>100</v>
-      </c>
-      <c r="X22">
-        <v>100</v>
-      </c>
-      <c r="Y22">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -5858,40 +5269,40 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>95.5</v>
+      </c>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23">
         <v>95</v>
       </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
-      <c r="L23">
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>95.5</v>
       </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
-        <v>95</v>
-      </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5899,19 +5310,10 @@
       <c r="V23">
         <v>100</v>
       </c>
-      <c r="W23">
-        <v>100</v>
-      </c>
-      <c r="X23">
-        <v>100</v>
-      </c>
-      <c r="Y23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -5935,40 +5337,40 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
+        <v>100</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
         <v>85</v>
       </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>90.90000000000001</v>
       </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>90</v>
-      </c>
-      <c r="R24">
-        <v>85</v>
-      </c>
       <c r="S24">
         <v>100</v>
       </c>
       <c r="T24">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5976,19 +5378,10 @@
       <c r="V24">
         <v>100</v>
       </c>
-      <c r="W24">
-        <v>100</v>
-      </c>
-      <c r="X24">
-        <v>100</v>
-      </c>
-      <c r="Y24">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -6012,40 +5405,40 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <v>100</v>
+      </c>
+      <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
         <v>80</v>
       </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>90.90000000000001</v>
       </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
-      <c r="Q25">
-        <v>90</v>
-      </c>
-      <c r="R25">
-        <v>80</v>
-      </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6053,19 +5446,10 @@
       <c r="V25">
         <v>100</v>
       </c>
-      <c r="W25">
-        <v>100</v>
-      </c>
-      <c r="X25">
-        <v>100</v>
-      </c>
-      <c r="Y25">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>70</v>
@@ -6089,60 +5473,51 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>93.2</v>
+      </c>
+      <c r="L26">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M26">
+        <v>95.2</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
         <v>75</v>
       </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>93.2</v>
       </c>
-      <c r="M26">
+      <c r="S26">
         <v>90.59999999999999</v>
       </c>
-      <c r="N26">
+      <c r="T26">
         <v>95.2</v>
       </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>90</v>
-      </c>
-      <c r="R26">
-        <v>75</v>
-      </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
-        <v>93.2</v>
-      </c>
       <c r="U26">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>95.2</v>
-      </c>
-      <c r="W26">
-        <v>100</v>
-      </c>
-      <c r="X26">
-        <v>100</v>
-      </c>
-      <c r="Y26">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>80</v>
@@ -6166,40 +5541,40 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>95.5</v>
+      </c>
+      <c r="L27">
+        <v>100</v>
+      </c>
+      <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
+        <v>100</v>
+      </c>
+      <c r="P27">
         <v>70</v>
       </c>
-      <c r="K27">
-        <v>100</v>
-      </c>
-      <c r="L27">
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>95.5</v>
       </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
-      <c r="O27">
-        <v>100</v>
-      </c>
-      <c r="P27">
-        <v>100</v>
-      </c>
-      <c r="Q27">
-        <v>80</v>
-      </c>
-      <c r="R27">
-        <v>70</v>
-      </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6207,19 +5582,10 @@
       <c r="V27">
         <v>100</v>
       </c>
-      <c r="W27">
-        <v>100</v>
-      </c>
-      <c r="X27">
-        <v>100</v>
-      </c>
-      <c r="Y27">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25">
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -6243,60 +5609,51 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
+        <v>93.8</v>
+      </c>
+      <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
         <v>95</v>
       </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>88.59999999999999</v>
       </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
+        <v>100</v>
+      </c>
+      <c r="U28">
         <v>93.8</v>
       </c>
-      <c r="P28">
-        <v>100</v>
-      </c>
-      <c r="Q28">
-        <v>90</v>
-      </c>
-      <c r="R28">
-        <v>95</v>
-      </c>
-      <c r="S28">
-        <v>100</v>
-      </c>
-      <c r="T28">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="U28">
-        <v>100</v>
-      </c>
       <c r="V28">
         <v>100</v>
       </c>
-      <c r="W28">
-        <v>93.8</v>
-      </c>
-      <c r="X28">
-        <v>100</v>
-      </c>
-      <c r="Y28">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>80</v>
@@ -6320,60 +5677,51 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L29">
+        <v>93.8</v>
+      </c>
+      <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
+        <v>100</v>
+      </c>
+      <c r="P29">
         <v>85</v>
       </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
-      <c r="L29">
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>90.90000000000001</v>
       </c>
-      <c r="M29">
+      <c r="S29">
         <v>93.8</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
-      <c r="P29">
-        <v>100</v>
-      </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
-        <v>85</v>
-      </c>
-      <c r="S29">
-        <v>100</v>
-      </c>
       <c r="T29">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U29">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V29">
         <v>100</v>
       </c>
-      <c r="W29">
-        <v>100</v>
-      </c>
-      <c r="X29">
-        <v>100</v>
-      </c>
-      <c r="Y29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>70</v>
@@ -6397,60 +5745,51 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>95.5</v>
+      </c>
+      <c r="L30">
+        <v>93.8</v>
+      </c>
+      <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
+        <v>100</v>
+      </c>
+      <c r="O30">
+        <v>100</v>
+      </c>
+      <c r="P30">
         <v>85</v>
       </c>
-      <c r="K30">
-        <v>100</v>
-      </c>
-      <c r="L30">
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>95.5</v>
       </c>
-      <c r="M30">
+      <c r="S30">
         <v>93.8</v>
       </c>
-      <c r="N30">
-        <v>100</v>
-      </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
-      <c r="P30">
-        <v>100</v>
-      </c>
-      <c r="Q30">
-        <v>90</v>
-      </c>
-      <c r="R30">
-        <v>85</v>
-      </c>
-      <c r="S30">
-        <v>100</v>
-      </c>
       <c r="T30">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="U30">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V30">
         <v>100</v>
       </c>
-      <c r="W30">
-        <v>100</v>
-      </c>
-      <c r="X30">
-        <v>100</v>
-      </c>
-      <c r="Y30">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25">
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>70</v>
@@ -6474,60 +5813,51 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>93.2</v>
+      </c>
+      <c r="L31">
+        <v>93.8</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="P31">
         <v>70</v>
       </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
-      <c r="L31">
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>93.2</v>
       </c>
-      <c r="M31">
+      <c r="S31">
         <v>93.8</v>
       </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
-      <c r="P31">
-        <v>100</v>
-      </c>
-      <c r="Q31">
-        <v>90</v>
-      </c>
-      <c r="R31">
-        <v>70</v>
-      </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
       <c r="T31">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="U31">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V31">
         <v>100</v>
       </c>
-      <c r="W31">
-        <v>100</v>
-      </c>
-      <c r="X31">
-        <v>100</v>
-      </c>
-      <c r="Y31">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25">
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>60</v>
@@ -6551,60 +5881,51 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>79.5</v>
+      </c>
+      <c r="L32">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O32">
+        <v>100</v>
+      </c>
+      <c r="P32">
         <v>75</v>
       </c>
-      <c r="K32">
-        <v>100</v>
-      </c>
-      <c r="L32">
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>79.5</v>
       </c>
-      <c r="M32">
+      <c r="S32">
         <v>71.90000000000001</v>
       </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
-      <c r="O32">
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
         <v>96.90000000000001</v>
       </c>
-      <c r="P32">
-        <v>100</v>
-      </c>
-      <c r="Q32">
-        <v>80</v>
-      </c>
-      <c r="R32">
-        <v>75</v>
-      </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-      <c r="T32">
-        <v>79.5</v>
-      </c>
-      <c r="U32">
-        <v>71.90000000000001</v>
-      </c>
       <c r="V32">
         <v>100</v>
       </c>
-      <c r="W32">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X32">
-        <v>100</v>
-      </c>
-      <c r="Y32">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -6628,60 +5949,51 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>97.7</v>
+      </c>
+      <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
+        <v>95.2</v>
+      </c>
+      <c r="N33">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="P33">
         <v>95</v>
       </c>
-      <c r="K33">
-        <v>100</v>
-      </c>
-      <c r="L33">
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>97.7</v>
       </c>
-      <c r="M33">
-        <v>100</v>
-      </c>
-      <c r="N33">
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>95.2</v>
       </c>
-      <c r="O33">
+      <c r="U33">
         <v>96.90000000000001</v>
       </c>
-      <c r="P33">
-        <v>100</v>
-      </c>
-      <c r="Q33">
-        <v>90</v>
-      </c>
-      <c r="R33">
-        <v>95</v>
-      </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
-        <v>97.7</v>
-      </c>
-      <c r="U33">
-        <v>100</v>
-      </c>
       <c r="V33">
-        <v>95.2</v>
-      </c>
-      <c r="W33">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X33">
-        <v>100</v>
-      </c>
-      <c r="Y33">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -6705,60 +6017,51 @@
         <v>50</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>43.2</v>
+      </c>
+      <c r="L34">
+        <v>81.3</v>
+      </c>
+      <c r="M34">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N34">
+        <v>12.5</v>
+      </c>
+      <c r="O34">
+        <v>25</v>
+      </c>
+      <c r="P34">
         <v>70</v>
       </c>
-      <c r="K34">
-        <v>100</v>
-      </c>
-      <c r="L34">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>43.2</v>
       </c>
-      <c r="M34">
+      <c r="S34">
         <v>81.3</v>
       </c>
-      <c r="N34">
+      <c r="T34">
         <v>92.90000000000001</v>
       </c>
-      <c r="O34">
+      <c r="U34">
         <v>12.5</v>
       </c>
-      <c r="P34">
+      <c r="V34">
         <v>25</v>
       </c>
-      <c r="Q34">
-        <v>80</v>
-      </c>
-      <c r="R34">
-        <v>70</v>
-      </c>
-      <c r="S34">
-        <v>100</v>
-      </c>
-      <c r="T34">
-        <v>43.2</v>
-      </c>
-      <c r="U34">
-        <v>81.3</v>
-      </c>
-      <c r="V34">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="W34">
-        <v>12.5</v>
-      </c>
-      <c r="X34">
-        <v>25</v>
-      </c>
-      <c r="Y34">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35">
         <v>70</v>
@@ -6782,60 +6085,51 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="L35">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
         <v>75</v>
       </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
-      <c r="L35">
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>90.90000000000001</v>
       </c>
-      <c r="M35">
+      <c r="S35">
         <v>84.40000000000001</v>
       </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
-      <c r="O35">
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
         <v>96.90000000000001</v>
       </c>
-      <c r="P35">
-        <v>100</v>
-      </c>
-      <c r="Q35">
-        <v>90</v>
-      </c>
-      <c r="R35">
-        <v>75</v>
-      </c>
-      <c r="S35">
-        <v>100</v>
-      </c>
-      <c r="T35">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="U35">
-        <v>84.40000000000001</v>
-      </c>
       <c r="V35">
         <v>100</v>
       </c>
-      <c r="W35">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X35">
-        <v>100</v>
-      </c>
-      <c r="Y35">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25">
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <v>80</v>
@@ -6859,40 +6153,40 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
+        <v>97.7</v>
+      </c>
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
+        <v>100</v>
+      </c>
+      <c r="O36">
+        <v>100</v>
+      </c>
+      <c r="P36">
         <v>85</v>
       </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
-      <c r="L36">
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>97.7</v>
       </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
-      <c r="N36">
-        <v>100</v>
-      </c>
-      <c r="O36">
-        <v>100</v>
-      </c>
-      <c r="P36">
-        <v>100</v>
-      </c>
-      <c r="Q36">
-        <v>90</v>
-      </c>
-      <c r="R36">
-        <v>85</v>
-      </c>
       <c r="S36">
         <v>100</v>
       </c>
       <c r="T36">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -6900,19 +6194,10 @@
       <c r="V36">
         <v>100</v>
       </c>
-      <c r="W36">
-        <v>100</v>
-      </c>
-      <c r="X36">
-        <v>100</v>
-      </c>
-      <c r="Y36">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25">
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37">
         <v>70</v>
@@ -6936,40 +6221,40 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L37">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="M37">
+        <v>100</v>
+      </c>
+      <c r="N37">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
         <v>75</v>
       </c>
-      <c r="K37">
-        <v>100</v>
-      </c>
-      <c r="L37">
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
         <v>88.59999999999999</v>
       </c>
-      <c r="M37">
+      <c r="S37">
         <v>96.90000000000001</v>
       </c>
-      <c r="N37">
-        <v>100</v>
-      </c>
-      <c r="O37">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="P37">
-        <v>100</v>
-      </c>
-      <c r="Q37">
-        <v>100</v>
-      </c>
-      <c r="R37">
-        <v>75</v>
-      </c>
-      <c r="S37">
-        <v>100</v>
-      </c>
       <c r="T37">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="U37">
         <v>96.90000000000001</v>
@@ -6977,21 +6262,12 @@
       <c r="V37">
         <v>100</v>
       </c>
-      <c r="W37">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="X37">
-        <v>100</v>
-      </c>
-      <c r="Y37">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7012,31 +6288,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7201,7 +6477,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -7210,19 +6486,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>67.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>32.4</v>
+        <v>17.6</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7233,7 +6509,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -7242,19 +6518,19 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>82.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G8" s="2">
-        <v>17.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7265,33 +6541,21 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2">
-        <v>91.2</v>
-      </c>
-      <c r="G9" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H9">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7326,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -7336,7 +6600,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7360,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7377,7 +6641,7 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7400,7 +6664,7 @@
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7414,22 +6678,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920180</v>
+        <v>24330051920174</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7437,22 +6701,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920180</v>
+        <v>24330051920174</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7460,16 +6724,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920184</v>
+        <v>24330051920180</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7483,22 +6747,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920184</v>
+        <v>24330051920180</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7506,22 +6770,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920206</v>
+        <v>24330051920182</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7529,16 +6793,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920206</v>
+        <v>24330051920182</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7552,16 +6816,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920277</v>
+        <v>24330051920206</v>
       </c>
       <c r="B10" t="s">
         <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -7575,16 +6839,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920277</v>
+        <v>24330051920206</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7598,16 +6862,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920190</v>
+        <v>24330051920277</v>
       </c>
       <c r="B12" t="s">
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -7621,24 +6885,93 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920190</v>
+        <v>24330051920277</v>
       </c>
       <c r="B13" t="s">
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920190</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
         <v>63</v>
       </c>
-      <c r="G13">
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920184</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="130">
   <si>
     <t>Materia</t>
   </si>
@@ -236,6 +236,45 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -245,9 +284,6 @@
     <t>HILARIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>PORTUGAL</t>
   </si>
   <si>
@@ -260,6 +296,39 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -281,6 +350,45 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>JHOCELIN VALENTINA</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>KEVIN JESUS</t>
+  </si>
+  <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
     <t>LIA SARED</t>
   </si>
   <si>
@@ -291,9 +399,6 @@
   </si>
   <si>
     <t>AMISADAY</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>GAEL ARMANDO</t>
@@ -6600,7 +6705,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6632,16 +6737,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920170</v>
+        <v>24330051920400</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6655,16 +6760,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920170</v>
+        <v>24330051920400</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6678,22 +6783,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920174</v>
+        <v>24330051920400</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6701,22 +6806,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920174</v>
+        <v>24330051920400</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6724,16 +6829,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920180</v>
+        <v>24330051920213</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6747,22 +6852,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920180</v>
+        <v>24330051920213</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6770,22 +6875,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920182</v>
+        <v>24330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6793,22 +6898,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920182</v>
+        <v>24330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6816,16 +6921,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920206</v>
+        <v>24330051920187</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6839,22 +6944,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920206</v>
+        <v>24330051920187</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6862,22 +6967,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920277</v>
+        <v>24330051920187</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6885,22 +6990,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920277</v>
+        <v>24330051920187</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6908,16 +7013,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920190</v>
+        <v>24330051920201</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -6931,22 +7036,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920190</v>
+        <v>24330051920201</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6954,24 +7059,1059 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
+        <v>24330051920201</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920201</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920194</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920194</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920194</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920194</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920202</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920202</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920202</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920308</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920308</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920308</v>
+      </c>
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920355</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>24330051920355</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920355</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>24330051920179</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>24330051920179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>24330051920388</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>24330051920388</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>24330051920388</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>23330051920298</v>
+      </c>
+      <c r="B38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920298</v>
+      </c>
+      <c r="B39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>23330051920298</v>
+      </c>
+      <c r="B40" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>24330051920188</v>
+      </c>
+      <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>24330051920188</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>24330051920188</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>24330051920316</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>61</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>24330051920316</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" t="s">
+        <v>6</v>
+      </c>
+      <c r="F45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>24330051920316</v>
+      </c>
+      <c r="B46" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" t="s">
+        <v>122</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>24330051920170</v>
+      </c>
+      <c r="B47" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>24330051920170</v>
+      </c>
+      <c r="B48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>24330051920174</v>
+      </c>
+      <c r="B49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>24330051920174</v>
+      </c>
+      <c r="B50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" t="s">
+        <v>124</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>60</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>24330051920180</v>
+      </c>
+      <c r="B51" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>24330051920180</v>
+      </c>
+      <c r="B52" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" t="s">
+        <v>63</v>
+      </c>
+      <c r="G52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>24330051920182</v>
+      </c>
+      <c r="B53" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>62</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>24330051920182</v>
+      </c>
+      <c r="B54" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" t="s">
+        <v>126</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>24330051920206</v>
+      </c>
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>24330051920206</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" t="s">
+        <v>116</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>60</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>24330051920277</v>
+      </c>
+      <c r="B57" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" t="s">
+        <v>127</v>
+      </c>
+      <c r="E57" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>24330051920277</v>
+      </c>
+      <c r="B58" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>24330051920190</v>
+      </c>
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>24330051920190</v>
+      </c>
+      <c r="B60" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>63</v>
+      </c>
+      <c r="G60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
         <v>24330051920184</v>
       </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="B61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" t="s">
+        <v>129</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
         <v>61</v>
       </c>
-      <c r="G16">
+      <c r="G61">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -200,27 +200,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -239,175 +239,172 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>MAZA</t>
   </si>
   <si>
-    <t>PELLICO</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>PICHARDO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
     <t>PORTUGAL</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>ZOPILLAXTLE</t>
   </si>
   <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>VEGA</t>
   </si>
   <si>
     <t>TLAXCALTECA</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>SANDY CAMILA</t>
   </si>
   <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>IRVING EMILIO</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
     <t>AYLIN ABIGAIL</t>
   </si>
   <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
     <t>LUZ ARIANA</t>
   </si>
   <si>
     <t>BETZY AYELEN</t>
   </si>
   <si>
-    <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
+    <t>LIA SARED</t>
   </si>
   <si>
     <t>JHOCELIN VALENTINA</t>
   </si>
   <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
     <t>KEVIN JESUS</t>
   </si>
   <si>
-    <t>BENJAMIN</t>
+    <t>SANDRA PAOLA</t>
   </si>
   <si>
     <t>JIMENA</t>
   </si>
   <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
-  </si>
-  <si>
     <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -958,13 +955,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -979,13 +976,13 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -1047,13 +1044,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1068,13 +1065,13 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>9</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>9</v>
@@ -1136,13 +1133,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1163,7 +1160,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>5</v>
@@ -1225,13 +1222,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1246,13 +1243,13 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -1314,13 +1311,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1335,13 +1332,13 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1403,13 +1400,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1492,13 +1489,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1516,10 +1513,10 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1581,13 +1578,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1608,7 +1605,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1670,13 +1667,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1759,13 +1756,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1780,13 +1777,13 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -1848,13 +1845,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1869,13 +1866,13 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>9</v>
@@ -1937,13 +1934,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1964,7 +1961,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>5</v>
@@ -2026,13 +2023,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2047,13 +2044,13 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2115,13 +2112,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2139,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2204,13 +2201,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2225,13 +2222,13 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2293,13 +2290,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2314,13 +2311,13 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2382,13 +2379,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2403,7 +2400,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2471,13 +2468,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2560,13 +2557,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2587,7 +2584,7 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>8</v>
@@ -2649,13 +2646,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2738,13 +2735,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2762,10 +2759,10 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2827,13 +2824,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2851,10 +2848,10 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2916,13 +2913,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2940,10 +2937,10 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>5</v>
@@ -3005,13 +3002,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3026,13 +3023,13 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3094,13 +3091,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3118,10 +3115,10 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>8</v>
@@ -3183,13 +3180,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3210,7 +3207,7 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3272,13 +3269,13 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3296,10 +3293,10 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>5</v>
@@ -3361,13 +3358,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3385,10 +3382,10 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>5</v>
@@ -3450,13 +3447,13 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -3539,13 +3536,13 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -3628,13 +3625,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -3717,13 +3714,13 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -3741,10 +3738,10 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>6</v>
@@ -3806,13 +3803,13 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>-1</v>
@@ -3827,7 +3824,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3895,13 +3892,13 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>-1</v>
@@ -3916,13 +3913,13 @@
         <v>6</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>5</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>5</v>
@@ -4109,10 +4106,10 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S4">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T4">
         <v>97.59999999999999</v>
@@ -4245,7 +4242,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4313,7 +4310,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4381,7 +4378,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4449,7 +4446,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4517,10 +4514,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S10">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4585,10 +4582,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>84.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="S11">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T11">
         <v>97.59999999999999</v>
@@ -4650,13 +4647,13 @@
         <v>55</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R12">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="S12">
-        <v>84.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="T12">
         <v>95.2</v>
@@ -4721,10 +4718,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>79.5</v>
+        <v>82.8</v>
       </c>
       <c r="S13">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4789,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4857,10 +4854,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S15">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T15">
         <v>97.59999999999999</v>
@@ -4925,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4993,10 +4990,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S17">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -5061,10 +5058,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>81.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S18">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T18">
         <v>97.59999999999999</v>
@@ -5129,10 +5126,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="S19">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -5197,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5265,7 +5262,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5333,7 +5330,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5401,7 +5398,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5469,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5537,7 +5534,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5605,10 +5602,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S26">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
         <v>95.2</v>
@@ -5673,7 +5670,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5741,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5809,10 +5806,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S29">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5877,10 +5874,10 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S30">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5945,10 +5942,10 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S31">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6010,13 +6007,13 @@
         <v>75</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R32">
-        <v>79.5</v>
+        <v>54.7</v>
       </c>
       <c r="S32">
-        <v>71.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6081,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6149,10 +6146,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>43.2</v>
+        <v>29.7</v>
       </c>
       <c r="S34">
-        <v>81.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T34">
         <v>92.90000000000001</v>
@@ -6217,10 +6214,10 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S35">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6285,7 +6282,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6353,10 +6350,10 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S37">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6422,7 +6419,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -6431,19 +6428,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
-        <v>35.3</v>
+        <v>38.2</v>
       </c>
       <c r="G2" s="2">
-        <v>64.7</v>
+        <v>61.8</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6454,7 +6451,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -6463,19 +6460,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="G3" s="2">
-        <v>61.8</v>
+        <v>47.1</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6486,7 +6483,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -6495,19 +6492,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>50</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>50</v>
+        <v>32.4</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6518,7 +6515,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -6527,19 +6524,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>52.9</v>
+        <v>76.5</v>
       </c>
       <c r="G5" s="2">
-        <v>47.1</v>
+        <v>23.5</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6550,7 +6547,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6559,19 +6556,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>67.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G6" s="2">
-        <v>32.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6582,7 +6579,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -6591,19 +6588,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>82.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G7" s="2">
-        <v>17.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6614,7 +6611,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -6635,7 +6632,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6705,7 +6702,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6746,13 +6743,13 @@
         <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6769,13 +6766,13 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6792,13 +6789,13 @@
         <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6806,22 +6803,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920400</v>
+        <v>24330051920355</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
         <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6829,7 +6826,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920213</v>
+        <v>24330051920355</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -6838,10 +6835,10 @@
         <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
@@ -6852,7 +6849,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920213</v>
+        <v>24330051920355</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
@@ -6861,10 +6858,10 @@
         <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
@@ -6878,16 +6875,16 @@
         <v>24330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
         <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>60</v>
@@ -6901,16 +6898,16 @@
         <v>24330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>63</v>
@@ -6921,19 +6918,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920187</v>
+        <v>24330051920213</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>61</v>
@@ -6944,22 +6941,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920187</v>
+        <v>24330051920394</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6967,22 +6964,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920187</v>
+        <v>24330051920394</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
         <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6990,22 +6987,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920187</v>
+        <v>24330051920394</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7013,13 +7010,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920201</v>
+        <v>24330051920406</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -7028,7 +7025,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7036,22 +7033,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920201</v>
+        <v>24330051920406</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7059,22 +7056,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920201</v>
+        <v>24330051920406</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7082,19 +7079,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920201</v>
+        <v>24330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>63</v>
@@ -7105,19 +7102,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920194</v>
+        <v>24330051920202</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
         <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>61</v>
@@ -7128,19 +7125,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920194</v>
+        <v>24330051920202</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
         <v>62</v>
@@ -7151,22 +7148,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920194</v>
+        <v>24330051920308</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -7174,22 +7171,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920194</v>
+        <v>24330051920308</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -7197,22 +7194,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920202</v>
+        <v>24330051920180</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -7220,22 +7217,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920202</v>
+        <v>24330051920180</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -7243,22 +7240,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920202</v>
+        <v>24330051920388</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -7266,22 +7263,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920202</v>
+        <v>24330051920388</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -7289,22 +7286,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920308</v>
+        <v>24330051920187</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -7312,22 +7309,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920308</v>
+        <v>24330051920187</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -7335,22 +7332,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920308</v>
+        <v>24330051920188</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -7358,19 +7355,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920355</v>
+        <v>24330051920188</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>61</v>
@@ -7381,22 +7378,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920355</v>
+        <v>24330051920190</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -7404,22 +7401,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920355</v>
+        <v>24330051920190</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -7427,22 +7424,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920179</v>
+        <v>24330051920201</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -7450,22 +7447,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920179</v>
+        <v>24330051920201</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -7473,22 +7470,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920179</v>
+        <v>24330051920194</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -7496,22 +7493,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920388</v>
+        <v>24330051920194</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -7519,22 +7516,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920388</v>
+        <v>24330051920170</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -7542,22 +7539,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920388</v>
+        <v>24330051920179</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -7568,16 +7565,16 @@
         <v>23330051920298</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F38" t="s">
         <v>62</v>
@@ -7588,19 +7585,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920298</v>
+        <v>24330051920184</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F39" t="s">
         <v>60</v>
@@ -7611,22 +7608,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920298</v>
+        <v>24330051920316</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -7634,22 +7631,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>24330051920188</v>
+        <v>24330051920206</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -7657,461 +7654,24 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>24330051920188</v>
+        <v>24330051920277</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
         <v>60</v>
       </c>
       <c r="G42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>24330051920188</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" t="s">
-        <v>121</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>63</v>
-      </c>
-      <c r="G43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>24330051920316</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>61</v>
-      </c>
-      <c r="G44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>24330051920316</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-      <c r="G45">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>24330051920316</v>
-      </c>
-      <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" t="s">
-        <v>122</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-      <c r="G46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>24330051920170</v>
-      </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" t="s">
-        <v>123</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>24330051920170</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" t="s">
-        <v>123</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-      <c r="G48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>24330051920174</v>
-      </c>
-      <c r="B49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" t="s">
-        <v>124</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>24330051920174</v>
-      </c>
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" t="s">
-        <v>124</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>60</v>
-      </c>
-      <c r="G50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>24330051920180</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>61</v>
-      </c>
-      <c r="G51">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>24330051920180</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>63</v>
-      </c>
-      <c r="G52">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>24330051920182</v>
-      </c>
-      <c r="B53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>24330051920182</v>
-      </c>
-      <c r="B54" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-      <c r="G54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>24330051920206</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>61</v>
-      </c>
-      <c r="G55">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>24330051920206</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-      <c r="G56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>24330051920277</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" t="s">
-        <v>127</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>61</v>
-      </c>
-      <c r="G57">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>24330051920277</v>
-      </c>
-      <c r="B58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>60</v>
-      </c>
-      <c r="G58">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>24330051920190</v>
-      </c>
-      <c r="B59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>61</v>
-      </c>
-      <c r="G59">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>24330051920190</v>
-      </c>
-      <c r="B60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" t="s">
-        <v>108</v>
-      </c>
-      <c r="D60" t="s">
-        <v>128</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>63</v>
-      </c>
-      <c r="G60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>24330051920184</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" t="s">
-        <v>129</v>
-      </c>
-      <c r="E61" t="s">
-        <v>5</v>
-      </c>
-      <c r="F61" t="s">
-        <v>61</v>
-      </c>
-      <c r="G61">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="127">
   <si>
     <t>Materia</t>
   </si>
@@ -203,21 +203,21 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
@@ -236,88 +236,106 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
   </si>
   <si>
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
     <t>VIEYRA</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
   </si>
   <si>
     <t>ORTEGA</t>
@@ -326,85 +344,61 @@
     <t>ZOPILLAXTLE</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
+    <t>YURANI</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>LIA SARED</t>
+  </si>
+  <si>
     <t>MARIEL</t>
   </si>
   <si>
-    <t>SANDY CAMILA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>SANDRA PAOLA</t>
   </si>
   <si>
     <t>IRVING EMILIO</t>
   </si>
   <si>
-    <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
     <t>AYLIN ABIGAIL</t>
   </si>
   <si>
     <t>BENJAMIN</t>
   </si>
   <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
     <t>OCTAVIO</t>
   </si>
   <si>
     <t>LUZ ARIANA</t>
-  </si>
-  <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>JHOCELIN VALENTINA</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -964,13 +958,13 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -985,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1053,13 +1047,13 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1142,13 +1136,13 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1163,10 +1157,10 @@
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1231,13 +1225,13 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1252,13 +1246,13 @@
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1320,13 +1314,13 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1341,13 +1335,13 @@
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1409,13 +1403,13 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1436,7 +1430,7 @@
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1498,13 +1492,13 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1525,7 +1519,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1587,13 +1581,13 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1608,13 +1602,13 @@
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1676,13 +1670,13 @@
         <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1700,10 +1694,10 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1765,13 +1759,13 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1789,7 +1783,7 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1854,13 +1848,13 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1875,13 +1869,13 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1943,13 +1937,13 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1964,13 +1958,13 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>9</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2032,13 +2026,13 @@
         <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -2053,13 +2047,13 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2121,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -2145,10 +2139,10 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2210,13 +2204,13 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2231,10 +2225,10 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2299,13 +2293,13 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2320,13 +2314,13 @@
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2388,13 +2382,13 @@
         <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2415,7 +2409,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2477,13 +2471,13 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2504,7 +2498,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2566,13 +2560,13 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2655,13 +2649,13 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2676,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2744,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2765,13 +2759,13 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2833,13 +2827,13 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2854,13 +2848,13 @@
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2922,13 +2916,13 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2943,10 +2937,10 @@
         <v>6</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -3011,13 +3005,13 @@
         <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -3035,10 +3029,10 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3100,13 +3094,13 @@
         <v>9</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3121,13 +3115,13 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>6</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3189,13 +3183,13 @@
         <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -3213,10 +3207,10 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3278,13 +3272,13 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3299,13 +3293,13 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3367,13 +3361,13 @@
         <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3388,13 +3382,13 @@
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3456,13 +3450,13 @@
         <v>5</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3545,13 +3539,13 @@
         <v>9</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3634,13 +3628,13 @@
         <v>5</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3723,13 +3717,13 @@
         <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>5</v>
@@ -3812,13 +3806,13 @@
         <v>9</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3836,7 +3830,7 @@
         <v>6</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -3901,13 +3895,13 @@
         <v>9</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3925,10 +3919,10 @@
         <v>5</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4112,10 +4106,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="T4">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>87.2</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4183,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4251,7 +4245,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4387,7 +4381,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4523,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4588,10 +4582,10 @@
         <v>95.8</v>
       </c>
       <c r="T11">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U11">
-        <v>96.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4656,10 +4650,10 @@
         <v>66.7</v>
       </c>
       <c r="T12">
-        <v>95.2</v>
+        <v>64.5</v>
       </c>
       <c r="U12">
-        <v>93.8</v>
+        <v>66</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4724,10 +4718,10 @@
         <v>95.8</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="U13">
-        <v>96.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4860,7 +4854,7 @@
         <v>93.8</v>
       </c>
       <c r="T15">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4928,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>76.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4999,7 +4993,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5064,10 +5058,10 @@
         <v>93.8</v>
       </c>
       <c r="T18">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5135,7 +5129,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>84.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5203,7 +5197,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5475,7 +5469,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5543,7 +5537,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5608,10 +5602,10 @@
         <v>93.8</v>
       </c>
       <c r="T26">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5679,7 +5673,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5744,10 +5738,10 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U28">
-        <v>93.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5815,7 +5809,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5951,7 +5945,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6016,13 +6010,13 @@
         <v>58.3</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>67.7</v>
       </c>
       <c r="U32">
-        <v>96.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="V32">
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6084,10 +6078,10 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U33">
-        <v>96.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -6152,13 +6146,13 @@
         <v>64.59999999999999</v>
       </c>
       <c r="T34">
-        <v>92.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="U34">
-        <v>12.5</v>
+        <v>10.6</v>
       </c>
       <c r="V34">
-        <v>25</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6223,7 +6217,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>96.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6291,7 +6285,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6359,7 +6353,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>96.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="V37">
         <v>100</v>
@@ -6451,7 +6445,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -6460,19 +6454,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>52.9</v>
+        <v>76.5</v>
       </c>
       <c r="G3" s="2">
-        <v>47.1</v>
+        <v>23.5</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6492,19 +6486,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>67.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>32.4</v>
+        <v>17.6</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6515,7 +6509,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -6524,19 +6518,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>76.5</v>
+        <v>85.3</v>
       </c>
       <c r="G5" s="2">
-        <v>23.5</v>
+        <v>14.7</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6547,7 +6541,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6556,19 +6550,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>91.2</v>
+        <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6579,7 +6573,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -6600,7 +6594,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6702,7 +6696,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6734,7 +6728,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920400</v>
+        <v>24330051920394</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
@@ -6743,7 +6737,7 @@
         <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6757,7 +6751,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920400</v>
+        <v>24330051920394</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
@@ -6766,13 +6760,13 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6780,7 +6774,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920400</v>
+        <v>24330051920394</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
@@ -6789,13 +6783,13 @@
         <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6803,22 +6797,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920355</v>
+        <v>24330051920394</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6826,7 +6820,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920355</v>
+        <v>24330051920213</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -6835,13 +6829,13 @@
         <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6849,7 +6843,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920355</v>
+        <v>24330051920213</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
@@ -6858,13 +6852,13 @@
         <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6875,19 +6869,19 @@
         <v>24330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6895,7 +6889,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920213</v>
+        <v>24330051920400</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
@@ -6904,13 +6898,13 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6918,7 +6912,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920213</v>
+        <v>24330051920400</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
@@ -6927,13 +6921,13 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6941,7 +6935,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920394</v>
+        <v>24330051920181</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
@@ -6950,7 +6944,7 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -6964,7 +6958,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920394</v>
+        <v>24330051920181</v>
       </c>
       <c r="B12" t="s">
         <v>75</v>
@@ -6973,10 +6967,10 @@
         <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -6987,22 +6981,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920394</v>
+        <v>24330051920388</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7010,22 +7004,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920406</v>
+        <v>24330051920388</v>
       </c>
       <c r="B14" t="s">
         <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7033,22 +7027,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920406</v>
+        <v>24330051920194</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7056,13 +7050,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920406</v>
+        <v>24330051920194</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
         <v>113</v>
@@ -7082,10 +7076,10 @@
         <v>24330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>114</v>
@@ -7094,7 +7088,7 @@
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7105,10 +7099,10 @@
         <v>24330051920202</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>114</v>
@@ -7117,7 +7111,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7125,22 +7119,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920202</v>
+        <v>24330051920308</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -7148,22 +7142,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920308</v>
+        <v>24330051920170</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -7171,22 +7165,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920308</v>
+        <v>24330051920355</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -7197,13 +7191,13 @@
         <v>24330051920180</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -7217,22 +7211,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920180</v>
+        <v>24330051920184</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -7240,16 +7234,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920388</v>
+        <v>24330051920406</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -7263,22 +7257,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920388</v>
+        <v>24330051920187</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -7286,16 +7280,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920187</v>
+        <v>24330051920188</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -7309,22 +7303,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920187</v>
+        <v>24330051920316</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -7332,16 +7326,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920188</v>
+        <v>24330051920206</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -7355,22 +7349,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920188</v>
+        <v>24330051920277</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -7381,13 +7375,13 @@
         <v>24330051920190</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -7401,277 +7395,24 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920190</v>
+        <v>24330051920201</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>24330051920201</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>24330051920201</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>24330051920194</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>24330051920194</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>24330051920170</v>
-      </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>24330051920179</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>23330051920298</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>24330051920184</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>24330051920316</v>
-      </c>
-      <c r="B40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>24330051920206</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>24330051920277</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20241.xlsx
+++ b/grupos/1BV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="111">
   <si>
     <t>Materia</t>
   </si>
@@ -242,57 +242,36 @@
     <t>GUERRA</t>
   </si>
   <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
     <t>OSORIO</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>PICHARDO</t>
   </si>
   <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
@@ -302,45 +281,33 @@
     <t>BRAVO</t>
   </si>
   <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
     <t>LIBRADO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>ZOPILLAXTLE</t>
   </si>
   <si>
@@ -350,34 +317,28 @@
     <t>SANDY CAMILA</t>
   </si>
   <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>YURANI</t>
   </si>
   <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
+    <t>AMISADAY</t>
   </si>
   <si>
     <t>IRVING EMILIO</t>
@@ -386,16 +347,7 @@
     <t>AYLIN ABIGAIL</t>
   </si>
   <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
     <t>JIMENA</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
   </si>
   <si>
     <t>LUZ ARIANA</t>
@@ -946,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -967,7 +919,7 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1035,7 +987,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -1056,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1124,7 +1076,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>7</v>
@@ -1213,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1234,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1302,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1391,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1480,7 +1432,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1501,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1569,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1658,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1747,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1836,7 +1788,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1857,7 +1809,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1925,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>6</v>
@@ -1946,7 +1898,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -2014,7 +1966,7 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -2035,7 +1987,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -2103,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -2124,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2192,7 +2144,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2281,7 +2233,7 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -2302,7 +2254,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2370,7 +2322,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2459,7 +2411,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2548,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2569,7 +2521,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2637,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2726,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>9</v>
@@ -2815,7 +2767,7 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2904,7 +2856,7 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>7</v>
@@ -2925,7 +2877,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2993,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -3082,7 +3034,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -3103,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -3171,7 +3123,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>6</v>
@@ -3192,7 +3144,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -3260,7 +3212,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3281,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3349,7 +3301,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -3438,7 +3390,7 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>5</v>
@@ -3527,7 +3479,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>8</v>
@@ -3616,7 +3568,7 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>5</v>
@@ -3705,7 +3657,7 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>6</v>
@@ -3794,7 +3746,7 @@
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>6</v>
@@ -3883,7 +3835,7 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -3904,7 +3856,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X37">
         <v>7</v>
@@ -4094,7 +4046,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4162,7 +4114,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4230,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4298,7 +4250,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4366,7 +4318,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4434,7 +4386,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4502,7 +4454,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4570,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>75</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4638,7 +4590,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>55</v>
+        <v>34.4</v>
       </c>
       <c r="Q12">
         <v>66.7</v>
@@ -4706,7 +4658,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4774,7 +4726,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4842,7 +4794,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4910,7 +4862,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4978,7 +4930,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5046,7 +4998,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5114,7 +5066,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5182,7 +5134,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5386,7 +5338,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5454,7 +5406,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>85</v>
+        <v>81.3</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5522,7 +5474,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5590,7 +5542,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5658,7 +5610,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5726,7 +5678,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5794,7 +5746,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5862,7 +5814,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5930,7 +5882,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5998,7 +5950,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q32">
         <v>66.7</v>
@@ -6066,7 +6018,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6134,7 +6086,7 @@
         <v>25</v>
       </c>
       <c r="P34">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6202,7 +6154,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6270,7 +6222,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6338,7 +6290,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6422,19 +6374,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="G2" s="2">
-        <v>61.8</v>
+        <v>47.1</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6696,7 +6648,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6734,10 +6686,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6757,10 +6709,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6780,10 +6732,10 @@
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -6803,10 +6755,10 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -6826,10 +6778,10 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6849,10 +6801,10 @@
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6872,10 +6824,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -6889,16 +6841,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920400</v>
+        <v>24330051920202</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -6912,22 +6864,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920400</v>
+        <v>24330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6935,22 +6887,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920181</v>
+        <v>24330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6958,22 +6910,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920181</v>
+        <v>24330051920308</v>
       </c>
       <c r="B12" t="s">
         <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6981,22 +6933,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920388</v>
+        <v>24330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7004,22 +6956,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920388</v>
+        <v>24330051920400</v>
       </c>
       <c r="B14" t="s">
         <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7027,22 +6979,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920194</v>
+        <v>24330051920400</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7050,22 +7002,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920194</v>
+        <v>24330051920388</v>
       </c>
       <c r="B16" t="s">
         <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7073,16 +7025,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920202</v>
+        <v>24330051920388</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -7096,22 +7048,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920202</v>
+        <v>24330051920194</v>
       </c>
       <c r="B18" t="s">
         <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7119,22 +7071,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920308</v>
+        <v>24330051920194</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -7142,16 +7094,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920170</v>
+        <v>24330051920355</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -7165,22 +7117,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920355</v>
+        <v>24330051920181</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -7188,16 +7140,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920180</v>
+        <v>24330051920182</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -7211,16 +7163,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920184</v>
+        <v>24330051920406</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -7234,16 +7186,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920406</v>
+        <v>24330051920187</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -7257,16 +7209,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920187</v>
+        <v>24330051920316</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -7280,16 +7232,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920188</v>
+        <v>24330051920201</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -7298,121 +7250,6 @@
         <v>60</v>
       </c>
       <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920316</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>24330051920206</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>24330051920277</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>24330051920190</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>24330051920201</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31">
         <v>5</v>
       </c>
     </row>
